--- a/data/trans_orig/IMC_inf_MED_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22726</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40461</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22079</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34839</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55054</t>
+          <t>54914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>74049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34023</t>
+          <t>34247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56246</t>
+          <t>56173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>76093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>16512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23193</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>29918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>50895</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27567</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47010</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49927</t>
+          <t>49377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>51878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62337</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85918</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>56826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75554</t>
+          <t>75609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56129</t>
+          <t>56387</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76386</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118289</t>
+          <t>118536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145576</t>
+          <t>147241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>22120</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>37422</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16847</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>20725</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23021</t>
+          <t>22794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>60611</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>41720</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35181</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>52126</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>81383</t>
+          <t>82298</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>106081</t>
+          <t>106000</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>29435</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>48566</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43487</t>
+          <t>43083</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>65235</t>
+          <t>65561</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>66300</t>
+          <t>67606</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>95186</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>117181</t>
+          <t>116489</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>152468</t>
+          <t>150916</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>66055</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>50121</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>74067</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>97317</t>
+          <t>98018</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>131574</t>
+          <t>131826</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>97340</t>
+          <t>97720</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>127440</t>
+          <t>126923</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>111435</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>144914</t>
+          <t>141535</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>218548</t>
+          <t>215641</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>260336</t>
+          <t>260321</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>227613</t>
+          <t>224785</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>262958</t>
+          <t>261529</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>193765</t>
+          <t>194202</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>231088</t>
+          <t>230464</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>433006</t>
+          <t>432858</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>482518</t>
+          <t>483469</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>24450</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22924</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>24928</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>42495</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36168</t>
+          <t>36489</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54719</t>
+          <t>54277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72570</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37103</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58577</t>
+          <t>58297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49939</t>
+          <t>50012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85174</t>
+          <t>86189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104815</t>
+          <t>105463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47478</t>
+          <t>46080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63886</t>
+          <t>63504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16948</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32159</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41904</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>58971</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>84212</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75586</t>
+          <t>73998</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95110</t>
+          <t>94871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63485</t>
+          <t>63932</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84256</t>
+          <t>83184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145286</t>
+          <t>143681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>172834</t>
+          <t>172163</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32123</t>
+          <t>31802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33044</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>36985</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52698</t>
+          <t>53409</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>67872</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38145</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>55849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>95509</t>
+          <t>94367</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>118717</t>
+          <t>118730</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57838</t>
+          <t>56881</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>36120</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>57366</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>60258</t>
+          <t>60107</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>86781</t>
+          <t>86973</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>46710</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72492</t>
+          <t>73156</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>81716</t>
+          <t>80079</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>113711</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>83348</t>
+          <t>82536</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>112302</t>
+          <t>110759</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>101927</t>
+          <t>103224</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>133052</t>
+          <t>133522</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>195098</t>
+          <t>192895</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>237436</t>
+          <t>237391</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>267204</t>
+          <t>266056</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>301627</t>
+          <t>299632</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>227663</t>
+          <t>226623</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>264498</t>
+          <t>263336</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>501892</t>
+          <t>503626</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>554936</t>
+          <t>556078</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>59376</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14030</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58122</t>
+          <t>57317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59521</t>
+          <t>59049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14260</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51497</t>
+          <t>50760</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57369</t>
+          <t>57479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90180</t>
+          <t>90354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97356</t>
+          <t>97720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143623</t>
+          <t>145509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31718</t>
+          <t>32401</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36303</t>
+          <t>37245</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>53453</t>
+          <t>53835</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46694</t>
+          <t>46416</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>47170</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>28880</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>50856</t>
+          <t>49448</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>43393</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69887</t>
+          <t>68583</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>58720</t>
+          <t>59445</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>83421</t>
+          <t>82536</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>88274</t>
+          <t>92618</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>131454</t>
+          <t>134877</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>159916</t>
+          <t>159633</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>202114</t>
+          <t>202725</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>150913</t>
+          <t>150700</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>184423</t>
+          <t>182388</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>318152</t>
+          <t>315362</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>376850</t>
+          <t>377240</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_MED_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Clase-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,19 +735,19 @@
         <v>6558</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3456</v>
+        <v>3156</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>11642</v>
+        <v>11904</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1140828005629941</v>
+        <v>0.09462028124300391</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.06012593931079296</v>
+        <v>0.04553257121146108</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2025246897377512</v>
+        <v>0.1717467881161284</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>13</v>
@@ -756,19 +756,19 @@
         <v>8702</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4945</v>
+        <v>4899</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>13795</v>
+        <v>14508</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1304596124088201</v>
+        <v>0.1140490625112533</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.07414309704838026</v>
+        <v>0.06420934535695137</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2068236479733317</v>
+        <v>0.1901476312016641</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>22</v>
@@ -777,19 +777,19 @@
         <v>15260</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10057</v>
+        <v>9556</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>21527</v>
+        <v>21846</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1228787768467969</v>
+        <v>0.104800862916451</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.08098059928772115</v>
+        <v>0.06562895301510641</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1733450978324783</v>
+        <v>0.1500305412474102</v>
       </c>
     </row>
     <row r="5">
@@ -806,61 +806,61 @@
         <v>5971</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3141</v>
+        <v>2716</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>10345</v>
+        <v>10681</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1038617024291998</v>
+        <v>0.08614290187241302</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.05464119892080341</v>
+        <v>0.03918973497011638</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1799630471367456</v>
+        <v>0.1541048254660811</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>6202</v>
+        <v>7460</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3291</v>
+        <v>3747</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>11867</v>
+        <v>12947</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.09298990002861746</v>
+        <v>0.09777181368996724</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.049346314900482</v>
+        <v>0.04910929004666188</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.177920364602337</v>
+        <v>0.1696847435426696</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>12173</v>
+        <v>13430</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>7707</v>
+        <v>8087</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>19103</v>
+        <v>19652</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.09802246357257911</v>
+        <v>0.0922363919836737</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.06205886778776858</v>
+        <v>0.05554208712323437</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.153824014206059</v>
+        <v>0.1349631885677932</v>
       </c>
     </row>
     <row r="6">
@@ -871,67 +871,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15932</v>
+        <v>20196</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>11142</v>
+        <v>14530</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>22079</v>
+        <v>26800</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2771438834933109</v>
+        <v>0.2913810635031335</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1938171936062629</v>
+        <v>0.2096429900836111</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3840764773844935</v>
+        <v>0.3866622793292163</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>16395</v>
+        <v>18786</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>11017</v>
+        <v>13382</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>23158</v>
+        <v>26057</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.24580887402678</v>
+        <v>0.2462138177586699</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1651665436068446</v>
+        <v>0.1753943420488146</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3471979457621386</v>
+        <v>0.3415101440453727</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>32327</v>
+        <v>38981</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>24378</v>
+        <v>30770</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>41662</v>
+        <v>48849</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2603138678153454</v>
+        <v>0.2677136585374078</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1963055042512588</v>
+        <v>0.211319126291079</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3354800737055605</v>
+        <v>0.3354806338319745</v>
       </c>
     </row>
     <row r="7">
@@ -942,67 +942,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>28425</v>
+        <v>35985</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>22625</v>
+        <v>29506</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>34924</v>
+        <v>42511</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4944682939829799</v>
+        <v>0.5191940635710131</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3935707510667061</v>
+        <v>0.4257125982968768</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6075290062236558</v>
+        <v>0.6133457429350507</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>35400</v>
+        <v>41351</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>28207</v>
+        <v>34341</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>41828</v>
+        <v>48745</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5307416135357825</v>
+        <v>0.5419653060401096</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4228869470916064</v>
+        <v>0.4500899196108612</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.6271083811791922</v>
+        <v>0.6388699992417232</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>63825</v>
+        <v>77336</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>55210</v>
+        <v>67090</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>73132</v>
+        <v>87894</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5139506731862662</v>
+        <v>0.5311260777597441</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4445734927239464</v>
+        <v>0.4607594994508876</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5888934442204926</v>
+        <v>0.6036334860903354</v>
       </c>
     </row>
     <row r="8">
@@ -1022,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4280</v>
+        <v>3001</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01044331953151541</v>
+        <v>0.008661689810436489</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.07445028020683832</v>
+        <v>0.0433050786814165</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
@@ -1056,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>3178</v>
+        <v>3457</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.004834218579012456</v>
+        <v>0.004123008802723536</v>
       </c>
       <c r="V8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.02558993610867459</v>
+        <v>0.02374439791780038</v>
       </c>
     </row>
     <row r="9">
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>57486</v>
+        <v>69310</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1097,16 +1097,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>66700</v>
+        <v>76298</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1118,16 +1118,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>124186</v>
+        <v>145608</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1157,19 +1157,19 @@
         <v>10010</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5934</v>
+        <v>5792</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>15386</v>
+        <v>15813</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1457461616675708</v>
+        <v>0.1247685383100651</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.08639614505653437</v>
+        <v>0.07219739992725314</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.2240220343891907</v>
+        <v>0.1970944393155495</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>9</v>
@@ -1178,19 +1178,19 @@
         <v>6761</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3242</v>
+        <v>3144</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>11854</v>
+        <v>11552</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.09597541034961507</v>
+        <v>0.08720539332706753</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.04602634426109368</v>
+        <v>0.04054702791482846</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1682769834177472</v>
+        <v>0.1490054878055175</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>23</v>
@@ -1199,19 +1199,19 @@
         <v>16771</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>10852</v>
+        <v>10979</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>23464</v>
+        <v>24660</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1205453679164522</v>
+        <v>0.1063083744079264</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.07799830902307509</v>
+        <v>0.06959562659508249</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1686519258146525</v>
+        <v>0.1563142926762978</v>
       </c>
     </row>
     <row r="11">
@@ -1222,25 +1222,25 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>7993</v>
+        <v>8771</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>4520</v>
+        <v>4689</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>12711</v>
+        <v>13723</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1163769362478127</v>
+        <v>0.1093172823061929</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.06580827989101093</v>
+        <v>0.05844547284210719</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1850723790097492</v>
+        <v>0.1710450264260605</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>10</v>
@@ -1249,40 +1249,40 @@
         <v>6582</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3411</v>
+        <v>3352</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>11178</v>
+        <v>11046</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.09342793265549577</v>
+        <v>0.08489069841200177</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.04841925700057449</v>
+        <v>0.04323044565635165</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1586799612516404</v>
+        <v>0.1424722830252603</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>14575</v>
+        <v>15352</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>9760</v>
+        <v>9907</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>21603</v>
+        <v>21852</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1047569970062081</v>
+        <v>0.09731299612461224</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.07014980530371562</v>
+        <v>0.06280052734028596</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1552756685575124</v>
+        <v>0.1385159799564968</v>
       </c>
     </row>
     <row r="12">
@@ -1293,67 +1293,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>20390</v>
+        <v>26125</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>14650</v>
+        <v>19870</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>26553</v>
+        <v>32662</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2968771916713242</v>
+        <v>0.325627329582808</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2133075058257246</v>
+        <v>0.2476600183737342</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.3866113977789713</v>
+        <v>0.4070993120864185</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>15281</v>
+        <v>16777</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>10066</v>
+        <v>11226</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>21760</v>
+        <v>22910</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2169170192014535</v>
+        <v>0.2163942389908167</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1428859731986482</v>
+        <v>0.1447929137510002</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.3088933684258326</v>
+        <v>0.2955014369973303</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>35671</v>
+        <v>42902</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>27922</v>
+        <v>33941</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>44325</v>
+        <v>52418</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2563903643408694</v>
+        <v>0.2719454358867918</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.2006939016949295</v>
+        <v>0.2151413253739177</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.3185931754027056</v>
+        <v>0.332263490879516</v>
       </c>
     </row>
     <row r="13">
@@ -1364,67 +1364,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>27297</v>
+        <v>32333</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>21325</v>
+        <v>25782</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>34660</v>
+        <v>39876</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3974464441767246</v>
+        <v>0.4030023182236282</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3104915364753105</v>
+        <v>0.3213556153812238</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5046473695752178</v>
+        <v>0.4970251722541965</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>38591</v>
+        <v>44179</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>31591</v>
+        <v>37122</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>45203</v>
+        <v>51492</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5478047201440857</v>
+        <v>0.5698266983624054</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4484358659095524</v>
+        <v>0.478807647569202</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.6416643723296822</v>
+        <v>0.6641596122298138</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>65888</v>
+        <v>76512</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>55705</v>
+        <v>66405</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>75515</v>
+        <v>86967</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4735784655163386</v>
+        <v>0.484987077530349</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4003864779567881</v>
+        <v>0.4209226981461944</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5427718868421932</v>
+        <v>0.5512620307491403</v>
       </c>
     </row>
     <row r="14">
@@ -1441,19 +1441,19 @@
         <v>2991</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>739</v>
+        <v>948</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7518</v>
+        <v>7366</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.04355326623656766</v>
+        <v>0.03728453157730579</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.01075471227777398</v>
+        <v>0.01181623666754808</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.1094542341209515</v>
+        <v>0.09180841000080199</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>5</v>
@@ -1462,19 +1462,19 @@
         <v>3232</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1191</v>
+        <v>1209</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>7141</v>
+        <v>7061</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.04587491764934999</v>
+        <v>0.04168297090770858</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.01690999773976064</v>
+        <v>0.01559507018461752</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1013672712467367</v>
+        <v>0.09107295774620282</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>9</v>
@@ -1483,19 +1483,19 @@
         <v>6223</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>3273</v>
+        <v>3257</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>11452</v>
+        <v>11502</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.04472880522013155</v>
+        <v>0.03944611605032051</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.02352785097152236</v>
+        <v>0.02064528935076169</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.08230998177538788</v>
+        <v>0.07290699831696026</v>
       </c>
     </row>
     <row r="15">
@@ -1506,16 +1506,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>68682</v>
+        <v>80230</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1527,16 +1527,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>70446</v>
+        <v>77530</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1548,16 +1548,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>139128</v>
+        <v>157760</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1587,19 +1587,19 @@
         <v>15934</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>10667</v>
+        <v>10042</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>22095</v>
+        <v>22277</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2606711319935129</v>
+        <v>0.2355089253219151</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1745122165763305</v>
+        <v>0.1484236595789316</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3614695807402376</v>
+        <v>0.3292757200367348</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>8</v>
@@ -1608,19 +1608,19 @@
         <v>5621</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2558</v>
+        <v>2654</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>10415</v>
+        <v>10151</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.09085298464149177</v>
+        <v>0.07832719104474405</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.04134910006831917</v>
+        <v>0.03698272408494387</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1683323350907642</v>
+        <v>0.1414533701388951</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>29</v>
@@ -1629,19 +1629,19 @@
         <v>21555</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>14751</v>
+        <v>15094</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>29235</v>
+        <v>29607</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1752490689877443</v>
+        <v>0.1546034221038387</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1199335836272201</v>
+        <v>0.1082651241556087</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2376951825511204</v>
+        <v>0.2123633753715579</v>
       </c>
     </row>
     <row r="17">
@@ -1658,61 +1658,61 @@
         <v>3129</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1151</v>
+        <v>1116</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>7025</v>
+        <v>6510</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.05119162140512957</v>
+        <v>0.04625016836505101</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.01883202592061841</v>
+        <v>0.01650202336023885</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1149313800073016</v>
+        <v>0.09622235391160482</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>6976</v>
+        <v>7743</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>3668</v>
+        <v>4244</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>12874</v>
+        <v>12851</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1127481747588811</v>
+        <v>0.1079042808997344</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.05928080277911522</v>
+        <v>0.05913510944332945</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.208087700237108</v>
+        <v>0.1790849010909809</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>10105</v>
+        <v>10873</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>5958</v>
+        <v>6567</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>16001</v>
+        <v>17844</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.08215584908629754</v>
+        <v>0.07798513440942902</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.048437530583402</v>
+        <v>0.04710140223191737</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1300961146862045</v>
+        <v>0.1279902425634076</v>
       </c>
     </row>
     <row r="18">
@@ -1723,67 +1723,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>17093</v>
+        <v>19811</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>11685</v>
+        <v>14352</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>23948</v>
+        <v>26245</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2796328256137846</v>
+        <v>0.2928134771973653</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1911606639329115</v>
+        <v>0.2121307351026502</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3917861424117494</v>
+        <v>0.3879233795269102</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>9609</v>
+        <v>12801</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>5570</v>
+        <v>7932</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>14619</v>
+        <v>18559</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1553041658069829</v>
+        <v>0.1783850781392212</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.09002902533759824</v>
+        <v>0.1105317258209975</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2362879741047856</v>
+        <v>0.2586201685970235</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>26701</v>
+        <v>32612</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>20403</v>
+        <v>25409</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>34820</v>
+        <v>41310</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2170929217398834</v>
+        <v>0.2339142211813142</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1658865078841567</v>
+        <v>0.1822523554928631</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2831013265747655</v>
+        <v>0.2962980063258414</v>
       </c>
     </row>
     <row r="19">
@@ -1794,67 +1794,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>23650</v>
+        <v>27463</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>17532</v>
+        <v>20899</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>29860</v>
+        <v>34162</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.3869117245104643</v>
+        <v>0.4059190443427329</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.2868199125733584</v>
+        <v>0.3089073510844438</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.4884961634060739</v>
+        <v>0.5049429571242491</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>36336</v>
+        <v>42268</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>29969</v>
+        <v>35540</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>42199</v>
+        <v>49477</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5872983841209778</v>
+        <v>0.5890039902478523</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4843873534715421</v>
+        <v>0.4952513651648351</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6820751518523988</v>
+        <v>0.6894586620149763</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>59985</v>
+        <v>69731</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>52177</v>
+        <v>59513</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>69701</v>
+        <v>78405</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.4877103854879718</v>
+        <v>0.5001576004206788</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4242225868995925</v>
+        <v>0.4268641773998232</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5667059751438926</v>
+        <v>0.5623730300289075</v>
       </c>
     </row>
     <row r="20">
@@ -1874,16 +1874,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4346</v>
+        <v>4804</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02159269647710861</v>
+        <v>0.01950838477293567</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.07109118411103232</v>
+        <v>0.07100662139668937</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>5</v>
@@ -1892,19 +1892,19 @@
         <v>3328</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1264</v>
+        <v>1221</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>7079</v>
+        <v>7039</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.05379629067166648</v>
+        <v>0.04637945966844809</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.02043730094070798</v>
+        <v>0.01701692891362223</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1144183161264678</v>
+        <v>0.09809423651736655</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>7</v>
@@ -1913,19 +1913,19 @@
         <v>4648</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>1921</v>
+        <v>2028</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>8832</v>
+        <v>9450</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.03779177469810291</v>
+        <v>0.03333962188473922</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01562262054673106</v>
+        <v>0.01454492056548302</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.07180870835903751</v>
+        <v>0.06778201798685375</v>
       </c>
     </row>
     <row r="21">
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>61126</v>
+        <v>67656</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1957,16 +1957,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>61869</v>
+        <v>71762</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1978,16 +1978,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>122994</v>
+        <v>139419</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2017,19 +2017,19 @@
         <v>24014</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>17171</v>
+        <v>17389</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>32301</v>
+        <v>32435</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1544706589851503</v>
+        <v>0.127911620389868</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1104549812375058</v>
+        <v>0.09262111343310601</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.2077760914424952</v>
+        <v>0.1727670349411339</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>18</v>
@@ -2038,19 +2038,19 @@
         <v>12024</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>7132</v>
+        <v>6876</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>18048</v>
+        <v>17289</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.09127397940006952</v>
+        <v>0.07325780861734683</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.05413504654186048</v>
+        <v>0.04188987107011206</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1370031100149719</v>
+        <v>0.1053373806690216</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>52</v>
@@ -2059,19 +2059,19 @@
         <v>36038</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>27822</v>
+        <v>27037</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>46559</v>
+        <v>46631</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.1254824407612797</v>
+        <v>0.1024178778525016</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.09687499560836003</v>
+        <v>0.07683710905028643</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.162117599694713</v>
+        <v>0.1325218202911061</v>
       </c>
     </row>
     <row r="23">
@@ -2082,67 +2082,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>20888</v>
+        <v>26584</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>14945</v>
+        <v>19377</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>29454</v>
+        <v>35750</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1343620940268037</v>
+        <v>0.1416005635551</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.09613410877655587</v>
+        <v>0.1032125263585048</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1894673467069027</v>
+        <v>0.1904271724108205</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>18671</v>
+        <v>24039</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>12671</v>
+        <v>17447</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>26628</v>
+        <v>33183</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.141729436106304</v>
+        <v>0.1464613555487828</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.09618373422481838</v>
+        <v>0.106296359697127</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.2021336587109187</v>
+        <v>0.2021690928079347</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>39559</v>
+        <v>50623</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>30604</v>
+        <v>40765</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>50777</v>
+        <v>62397</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.137741482332212</v>
+        <v>0.1438679219624224</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.106562316258559</v>
+        <v>0.1158514108454083</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1768035036274802</v>
+        <v>0.1773301940556681</v>
       </c>
     </row>
     <row r="24">
@@ -2153,67 +2153,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>41918</v>
+        <v>49105</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>33453</v>
+        <v>39148</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>51364</v>
+        <v>59050</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2696370188624233</v>
+        <v>0.2615593058179844</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.2151898290261583</v>
+        <v>0.2085252766947678</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3304013766100034</v>
+        <v>0.3145320177234388</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>31000</v>
+        <v>36883</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>23940</v>
+        <v>28376</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>39984</v>
+        <v>46047</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2353153491205018</v>
+        <v>0.2247146838365654</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1817278694808241</v>
+        <v>0.1728868108419887</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3035196089386296</v>
+        <v>0.2805482368944773</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>72917</v>
+        <v>85988</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>60946</v>
+        <v>72608</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>86115</v>
+        <v>99106</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2538937225560567</v>
+        <v>0.2443728136737503</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.212212430938879</v>
+        <v>0.2063490414232467</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2998482666394088</v>
+        <v>0.2816540429450147</v>
       </c>
     </row>
     <row r="25">
@@ -2224,67 +2224,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>66576</v>
+        <v>85972</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>57728</v>
+        <v>73801</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>77681</v>
+        <v>97571</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4282558714613385</v>
+        <v>0.4579364909000623</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.3713362507274426</v>
+        <v>0.3931047322271088</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4996855581142399</v>
+        <v>0.519719086913037</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>65862</v>
+        <v>87007</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>56748</v>
+        <v>76474</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>75645</v>
+        <v>96886</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.4999522780167497</v>
+        <v>0.5301000344803611</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4307725252396138</v>
+        <v>0.4659292328190442</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.5742200225184255</v>
+        <v>0.5902902968578769</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>132438</v>
+        <v>172979</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>117712</v>
+        <v>157731</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>145941</v>
+        <v>188186</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.4611429011714603</v>
+        <v>0.4915977990678693</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4098695797162192</v>
+        <v>0.4482625100976189</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5081594708530398</v>
+        <v>0.5348160738239888</v>
       </c>
     </row>
     <row r="26">
@@ -2301,19 +2301,19 @@
         <v>2064</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>5468</v>
+        <v>5912</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01327435666428421</v>
+        <v>0.01099201933698531</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.004006816085687382</v>
+        <v>0.00336444825227399</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.03517159766372798</v>
+        <v>0.03148957025890015</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>7</v>
@@ -2322,19 +2322,19 @@
         <v>4180</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1766</v>
+        <v>1735</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>8138</v>
+        <v>8487</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03172895735637499</v>
+        <v>0.0254661175169438</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01340353319078984</v>
+        <v>0.01057367704718252</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.06177370564570106</v>
+        <v>0.05171110739844886</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>10</v>
@@ -2343,19 +2343,19 @@
         <v>6243</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>3182</v>
+        <v>3256</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>11403</v>
+        <v>11114</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.02173945317899117</v>
+        <v>0.01774358744345634</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.01107872089236275</v>
+        <v>0.009254114119297545</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.03970396591121521</v>
+        <v>0.03158639138386723</v>
       </c>
     </row>
     <row r="27">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>155459</v>
+        <v>187738</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2387,16 +2387,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>131736</v>
+        <v>164133</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2408,16 +2408,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>413</v>
+        <v>506</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>287195</v>
+        <v>351871</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2447,19 +2447,19 @@
         <v>15485</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>10178</v>
+        <v>9718</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>22523</v>
+        <v>22414</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.1569559641452889</v>
+        <v>0.1254565692826308</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1031608581473912</v>
+        <v>0.07873377420586117</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.22828820585838</v>
+        <v>0.1815960608449663</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>20</v>
@@ -2468,19 +2468,19 @@
         <v>13298</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>8575</v>
+        <v>8394</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>19816</v>
+        <v>19612</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.122542018865572</v>
+        <v>0.1022993318984491</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.07901783599633265</v>
+        <v>0.0645773515571985</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1826152539626296</v>
+        <v>0.1508727167750477</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>42</v>
@@ -2489,19 +2489,19 @@
         <v>28783</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>20571</v>
+        <v>21181</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>36910</v>
+        <v>38692</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.1389303290513914</v>
+        <v>0.1135782944142334</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.09929575445237887</v>
+        <v>0.08358265877134972</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1781589803133308</v>
+        <v>0.1526796534046388</v>
       </c>
     </row>
     <row r="29">
@@ -2512,67 +2512,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>14045</v>
+        <v>20214</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>9106</v>
+        <v>14227</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>21129</v>
+        <v>28450</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1423571214478307</v>
+        <v>0.1637699478377707</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09229964025975064</v>
+        <v>0.1152653201815558</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.2141610451583344</v>
+        <v>0.2304963772554567</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>10771</v>
+        <v>16065</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>6250</v>
+        <v>10467</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>17075</v>
+        <v>23028</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.09926267606511471</v>
+        <v>0.1235888631039885</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.05759833491121562</v>
+        <v>0.08052586424274057</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1573482432920258</v>
+        <v>0.1771581174254737</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>24816</v>
+        <v>36279</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>17461</v>
+        <v>27986</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>33680</v>
+        <v>47268</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1197847386324093</v>
+        <v>0.1431594595891053</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08428094542221767</v>
+        <v>0.1104348478729173</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1625698890354912</v>
+        <v>0.1865209987114985</v>
       </c>
     </row>
     <row r="30">
@@ -2583,67 +2583,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>18913</v>
+        <v>23876</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>13351</v>
+        <v>17585</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>25370</v>
+        <v>31735</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.1916999299268107</v>
+        <v>0.1934401905549439</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.1353269464111932</v>
+        <v>0.1424732001752769</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2571492525534593</v>
+        <v>0.2571126685647147</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>30347</v>
+        <v>38196</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>23207</v>
+        <v>29842</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>38424</v>
+        <v>47053</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.279654582813555</v>
+        <v>0.2938434475195632</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2138564565430266</v>
+        <v>0.2295765768809348</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.3540898014628392</v>
+        <v>0.3619821069557006</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>49260</v>
+        <v>62072</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>39025</v>
+        <v>51714</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>59779</v>
+        <v>73338</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2377695817746418</v>
+        <v>0.2449410437924177</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.1883665543820187</v>
+        <v>0.2040658858555671</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2885459181451265</v>
+        <v>0.2893940337470406</v>
       </c>
     </row>
     <row r="31">
@@ -2654,67 +2654,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>43347</v>
+        <v>56985</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>34537</v>
+        <v>47274</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>51320</v>
+        <v>65656</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4393601158754266</v>
+        <v>0.4616797966923051</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3500618393808601</v>
+        <v>0.3830060399988671</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5201740506554755</v>
+        <v>0.5319323089707034</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>50002</v>
+        <v>58332</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>42371</v>
+        <v>48883</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>58042</v>
+        <v>67640</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.4607830263958052</v>
+        <v>0.4487478464218261</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3904610589816402</v>
+        <v>0.3760541287751143</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.534875271933563</v>
+        <v>0.5203541042630258</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>93349</v>
+        <v>115317</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>81389</v>
+        <v>103140</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>105452</v>
+        <v>128209</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.4505811939747505</v>
+        <v>0.4550464812691915</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.3928534132120345</v>
+        <v>0.4069942240429515</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5090029094363354</v>
+        <v>0.5059190406135397</v>
       </c>
     </row>
     <row r="32">
@@ -2731,19 +2731,19 @@
         <v>6869</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3279</v>
+        <v>3514</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>12413</v>
+        <v>12529</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.06962686860464309</v>
+        <v>0.05565349563234949</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.03323690367018396</v>
+        <v>0.02847031457889992</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.1258158952531496</v>
+        <v>0.1015048541159546</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>6</v>
@@ -2752,19 +2752,19 @@
         <v>4097</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1875</v>
+        <v>1332</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>8518</v>
+        <v>8887</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03775769585995307</v>
+        <v>0.03152051105617312</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01727740848872521</v>
+        <v>0.0102453453194979</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07849480074659093</v>
+        <v>0.06836910718264923</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>15</v>
@@ -2773,19 +2773,19 @@
         <v>10967</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>6184</v>
+        <v>6407</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>17443</v>
+        <v>17076</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.05293415656680693</v>
+        <v>0.04327472093505209</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.02984852713443818</v>
+        <v>0.02528055829081646</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.08419517937050404</v>
+        <v>0.06738409939513061</v>
       </c>
     </row>
     <row r="33">
@@ -2796,16 +2796,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>98659</v>
+        <v>123430</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -2817,16 +2817,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>108515</v>
+        <v>129988</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -2838,16 +2838,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>207174</v>
+        <v>253418</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -2877,19 +2877,19 @@
         <v>7886</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>4102</v>
+        <v>4129</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>13435</v>
+        <v>12934</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.1458850106531393</v>
+        <v>0.1256316806885474</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.07588590595203885</v>
+        <v>0.06577418373245117</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.2485293777130665</v>
+        <v>0.2060495153897392</v>
       </c>
       <c r="J34" s="5" t="n">
         <v>11</v>
@@ -2898,19 +2898,19 @@
         <v>7170</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>3961</v>
+        <v>3711</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>11601</v>
+        <v>11515</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.1749914367373411</v>
+        <v>0.1593747657093416</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.09666239307834942</v>
+        <v>0.08247675305007239</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.2831415905014449</v>
+        <v>0.255940593409043</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>22</v>
@@ -2919,19 +2919,19 @@
         <v>15056</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>10090</v>
+        <v>10419</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>22315</v>
+        <v>22216</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>0.1584348108787234</v>
+        <v>0.1397192328204553</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>0.1061793260861954</v>
+        <v>0.09668759167675668</v>
       </c>
       <c r="W34" s="6" t="n">
-        <v>0.2348168456162321</v>
+        <v>0.2061627017742233</v>
       </c>
     </row>
     <row r="35">
@@ -2942,67 +2942,67 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>8937</v>
+        <v>9610</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>5072</v>
+        <v>5569</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>13956</v>
+        <v>14735</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.1653325996526766</v>
+        <v>0.1531022602698689</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.09382220983515041</v>
+        <v>0.08871322298836075</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.2581711062986655</v>
+        <v>0.2347393009012282</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>4463</v>
+        <v>6287</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>1788</v>
+        <v>2829</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>8973</v>
+        <v>11553</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1089330606187774</v>
+        <v>0.1397537510155283</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.04364145082714093</v>
+        <v>0.06288772664381251</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.2189859526821813</v>
+        <v>0.2567920170791123</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R35" s="5" t="n">
-        <v>13401</v>
+        <v>15898</v>
       </c>
       <c r="S35" s="5" t="n">
-        <v>7813</v>
+        <v>10485</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>19586</v>
+        <v>22556</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0.1410148443349036</v>
+        <v>0.1475293311826828</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>0.08221013799169724</v>
+        <v>0.09729678449390171</v>
       </c>
       <c r="W35" s="6" t="n">
-        <v>0.2060963933652885</v>
+        <v>0.2093164066940333</v>
       </c>
     </row>
     <row r="36">
@@ -3013,67 +3013,67 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>12482</v>
+        <v>16069</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>8349</v>
+        <v>11122</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>18440</v>
+        <v>22421</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.2309091738220408</v>
+        <v>0.2559959241631869</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.1544454810882832</v>
+        <v>0.1771778222672061</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.3411231237033223</v>
+        <v>0.3571845987625616</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>9242</v>
+        <v>10646</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>5021</v>
+        <v>6396</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>13818</v>
+        <v>15905</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2255604564154014</v>
+        <v>0.236646422325795</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.1225479190297484</v>
+        <v>0.1421622943591522</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.3372495472789526</v>
+        <v>0.3535219189054056</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="R36" s="5" t="n">
-        <v>21724</v>
+        <v>26716</v>
       </c>
       <c r="S36" s="5" t="n">
-        <v>15974</v>
+        <v>19811</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>29556</v>
+        <v>35115</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>0.2286029705553724</v>
+        <v>0.2479176137273533</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>0.1680953260432692</v>
+        <v>0.183845393113484</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>0.311014662533889</v>
+        <v>0.3258635433451624</v>
       </c>
     </row>
     <row r="37">
@@ -3084,67 +3084,67 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>22862</v>
+        <v>27316</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>16619</v>
+        <v>21099</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>28738</v>
+        <v>34311</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.4229272169067677</v>
+        <v>0.4351757162420712</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.3074427976519727</v>
+        <v>0.3361208799633174</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5316329534708863</v>
+        <v>0.546611212035762</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>18012</v>
+        <v>18799</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>12719</v>
+        <v>13176</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>23029</v>
+        <v>24533</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.4396044166127693</v>
+        <v>0.4178578225381335</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.310410067750214</v>
+        <v>0.2928778711944837</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.5620359035329033</v>
+        <v>0.545304502280423</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="R37" s="5" t="n">
-        <v>40875</v>
+        <v>46115</v>
       </c>
       <c r="S37" s="5" t="n">
-        <v>32251</v>
+        <v>37850</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>48241</v>
+        <v>55076</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0.4301179150717371</v>
+        <v>0.4279455910114139</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>0.3393716915306719</v>
+        <v>0.3512430501461765</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>0.5076364393067072</v>
+        <v>0.5110968715693058</v>
       </c>
     </row>
     <row r="38">
@@ -3161,19 +3161,19 @@
         <v>1889</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>5288</v>
+        <v>5410</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.0349459989653756</v>
+        <v>0.03009441863632547</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.01120192940137588</v>
+        <v>0.009543431501981798</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.0978309866656359</v>
+        <v>0.08619183410458277</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>3</v>
@@ -3182,19 +3182,19 @@
         <v>2086</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>5602</v>
+        <v>5524</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.05091062961571081</v>
+        <v>0.0463672384112015</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.01623149987869035</v>
+        <v>0.01454239868669846</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.1367148546751247</v>
+        <v>0.1227745041898214</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>6</v>
@@ -3203,19 +3203,19 @@
         <v>3975</v>
       </c>
       <c r="S38" s="5" t="n">
-        <v>1359</v>
+        <v>1871</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>8081</v>
+        <v>8606</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>0.04182945915926348</v>
+        <v>0.03688823125809478</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>0.01430121765091494</v>
+        <v>0.0173608604990405</v>
       </c>
       <c r="W38" s="6" t="n">
-        <v>0.08503507314449088</v>
+        <v>0.07986251370748781</v>
       </c>
     </row>
     <row r="39">
@@ -3226,16 +3226,16 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>54056</v>
+        <v>62771</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1</v>
@@ -3247,16 +3247,16 @@
         <v>1</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>40974</v>
+        <v>44989</v>
       </c>
       <c r="N39" s="6" t="n">
         <v>1</v>
@@ -3268,16 +3268,16 @@
         <v>1</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="R39" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="S39" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>95031</v>
+        <v>107760</v>
       </c>
       <c r="U39" s="6" t="n">
         <v>1</v>
@@ -3307,19 +3307,19 @@
         <v>79887</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>67457</v>
+        <v>66500</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>96007</v>
+        <v>94342</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.161235368517249</v>
+        <v>0.1351415997493141</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.1361487357013422</v>
+        <v>0.1124959539268014</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.1937703329883511</v>
+        <v>0.1595942801445357</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>79</v>
@@ -3328,19 +3328,19 @@
         <v>53576</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>43292</v>
+        <v>44136</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>65989</v>
+        <v>66541</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.1115600320170514</v>
+        <v>0.09487424972329288</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.09014630507847048</v>
+        <v>0.07815852485366639</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.1374082432203531</v>
+        <v>0.1178345892100422</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>190</v>
@@ -3349,19 +3349,19 @@
         <v>133463</v>
       </c>
       <c r="S40" s="5" t="n">
-        <v>116966</v>
+        <v>115945</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>150586</v>
+        <v>151399</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>0.1367853314463935</v>
+        <v>0.1154683748720618</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>0.1198777823673314</v>
+        <v>0.1003127954695662</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>0.1543348252606529</v>
+        <v>0.1309864193190119</v>
       </c>
     </row>
     <row r="41">
@@ -3372,67 +3372,67 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>60963</v>
+        <v>74278</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>49181</v>
+        <v>62164</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>73512</v>
+        <v>88205</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.1230404531103476</v>
+        <v>0.1256539693720443</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.0992607361207402</v>
+        <v>0.105160762139467</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.1483683930705661</v>
+        <v>0.1492131255447556</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>53665</v>
+        <v>68177</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>42538</v>
+        <v>54589</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>65276</v>
+        <v>80938</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.1117471212202444</v>
+        <v>0.1207302941207444</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.08857692557531471</v>
+        <v>0.09666915061977545</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1359242704772395</v>
+        <v>0.1433295153566183</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="R41" s="5" t="n">
-        <v>114628</v>
+        <v>142455</v>
       </c>
       <c r="S41" s="5" t="n">
-        <v>98407</v>
+        <v>124082</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>132050</v>
+        <v>161568</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>0.1174819123369922</v>
+        <v>0.1232484331155291</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>0.1008569924671237</v>
+        <v>0.107352217164417</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>0.1353378582671348</v>
+        <v>0.1397843857344264</v>
       </c>
     </row>
     <row r="42">
@@ -3443,67 +3443,67 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>126727</v>
+        <v>155181</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>110379</v>
+        <v>139819</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>142620</v>
+        <v>176361</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.2557729481300737</v>
+        <v>0.2625143018778072</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.2227763734009517</v>
+        <v>0.236526023701621</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.2878497798816776</v>
+        <v>0.2983438542450635</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>111873</v>
+        <v>134090</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>97291</v>
+        <v>118042</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>127764</v>
+        <v>150680</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.2329528838644902</v>
+        <v>0.2374528283978201</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.2025877589589668</v>
+        <v>0.2090341485384824</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.2660425485578877</v>
+        <v>0.2668322374717207</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>343</v>
+        <v>416</v>
       </c>
       <c r="R42" s="5" t="n">
-        <v>238601</v>
+        <v>289271</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>216128</v>
+        <v>266315</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>262085</v>
+        <v>314102</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>0.2445409876329243</v>
+        <v>0.2502701387230808</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>0.2215089650542572</v>
+        <v>0.2304086004689713</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>0.2686097435728912</v>
+        <v>0.2717528522277822</v>
       </c>
     </row>
     <row r="43">
@@ -3514,67 +3514,67 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>305</v>
+        <v>385</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>212158</v>
+        <v>266055</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>192709</v>
+        <v>243392</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>231942</v>
+        <v>283832</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.4281963702716561</v>
+        <v>0.4500743646327753</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.3889427279510441</v>
+        <v>0.4117365168334748</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.4681277933041014</v>
+        <v>0.4801467333600055</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>244203</v>
+        <v>291936</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>224890</v>
+        <v>272588</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>261679</v>
+        <v>311138</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.5085010310974373</v>
+        <v>0.5169743034828503</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.4682875693938787</v>
+        <v>0.4827118368253927</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.5448924468591434</v>
+        <v>0.5509788562473443</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>655</v>
+        <v>804</v>
       </c>
       <c r="R43" s="5" t="n">
-        <v>456360</v>
+        <v>557991</v>
       </c>
       <c r="S43" s="5" t="n">
-        <v>428947</v>
+        <v>530047</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>480278</v>
+        <v>586879</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0.4677220599294407</v>
+        <v>0.4827593449064075</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>0.4396260707122663</v>
+        <v>0.4585828343381351</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0.4922357613000073</v>
+        <v>0.5077529051730995</v>
       </c>
     </row>
     <row r="44">
@@ -3591,19 +3591,19 @@
         <v>15734</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>10254</v>
+        <v>10314</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>24482</v>
+        <v>23747</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.03175485997067354</v>
+        <v>0.02661576436805912</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.02069574408499699</v>
+        <v>0.01744746975890343</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.04941099121485198</v>
+        <v>0.04017247827728959</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>26</v>
@@ -3612,19 +3612,19 @@
         <v>16923</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>11086</v>
+        <v>11236</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>24404</v>
+        <v>24052</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.03523893180077679</v>
+        <v>0.02996832427529227</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.02308462991324491</v>
+        <v>0.01989662479041408</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.05081648980396258</v>
+        <v>0.04259270393276087</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>48</v>
@@ -3633,19 +3633,19 @@
         <v>32657</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>24440</v>
+        <v>24603</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>42948</v>
+        <v>42559</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0.03346970865424932</v>
+        <v>0.0282537083829207</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0.0250479766822861</v>
+        <v>0.02128561022520205</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>0.04401679222060737</v>
+        <v>0.03682138077765564</v>
       </c>
     </row>
     <row r="45">
@@ -3656,16 +3656,16 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>712</v>
+        <v>848</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>495468</v>
+        <v>591135</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>1</v>
@@ -3677,16 +3677,16 @@
         <v>1</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>689</v>
+        <v>811</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>480240</v>
+        <v>564701</v>
       </c>
       <c r="N45" s="6" t="n">
         <v>1</v>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>1401</v>
+        <v>1659</v>
       </c>
       <c r="R45" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="S45" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>975708</v>
+        <v>1155836</v>
       </c>
       <c r="U45" s="6" t="n">
         <v>1</v>
@@ -3781,7 +3781,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3971,19 +3971,19 @@
         <v>5903</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2718</v>
+        <v>2779</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>10560</v>
+        <v>10697</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.09113414499652807</v>
+        <v>0.07420449071667556</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.04196420749967186</v>
+        <v>0.03493543275880816</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1630284275180362</v>
+        <v>0.1344545880967622</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>5</v>
@@ -3992,19 +3992,19 @@
         <v>3337</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>7511</v>
+        <v>7546</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.06274460456755086</v>
+        <v>0.05281258240402442</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.02430480821029139</v>
+        <v>0.02037818643422468</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1412144772967866</v>
+        <v>0.1194118496548793</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>14</v>
@@ -4013,19 +4013,19 @@
         <v>9241</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>5481</v>
+        <v>5210</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>15322</v>
+        <v>14511</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.07833378388832954</v>
+        <v>0.06473469955078685</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.04646010327913624</v>
+        <v>0.03649678538442747</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1298855264433124</v>
+        <v>0.1016533136938351</v>
       </c>
     </row>
     <row r="5">
@@ -4036,67 +4036,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6634</v>
+        <v>7209</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3342</v>
+        <v>3845</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>11658</v>
+        <v>12198</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.102408540704249</v>
+        <v>0.0906176992910518</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.05159328004857127</v>
+        <v>0.04832457474872813</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1799786382576515</v>
+        <v>0.1533270640394362</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>4617</v>
+        <v>5085</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2032</v>
+        <v>2528</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>9390</v>
+        <v>10109</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.08679517276912423</v>
+        <v>0.08047303662409405</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.03819774384272971</v>
+        <v>0.04000815427012387</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1765441986256053</v>
+        <v>0.1599766874684383</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>11250</v>
+        <v>12294</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>6949</v>
+        <v>7499</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>18098</v>
+        <v>18107</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.09536873855652664</v>
+        <v>0.08612684997081313</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.05890367030403287</v>
+        <v>0.05253595720010096</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1534175561540437</v>
+        <v>0.1268479199494915</v>
       </c>
     </row>
     <row r="6">
@@ -4107,67 +4107,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>17517</v>
+        <v>21130</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12601</v>
+        <v>14761</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>23882</v>
+        <v>27822</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2704217574782097</v>
+        <v>0.2655983401875104</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1945248850930164</v>
+        <v>0.1855481594373387</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.368675397831957</v>
+        <v>0.3497162560852206</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>10789</v>
+        <v>13922</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>6289</v>
+        <v>9262</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>15835</v>
+        <v>19648</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2028372569937562</v>
+        <v>0.2203051125105865</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1182332606382745</v>
+        <v>0.1465687177588958</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.2977097425589875</v>
+        <v>0.3109304822237005</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>28306</v>
+        <v>35051</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>21618</v>
+        <v>27700</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>36919</v>
+        <v>44131</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.239949055263023</v>
+        <v>0.2455478892852008</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1832593467582818</v>
+        <v>0.1940495563871812</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3129613740885264</v>
+        <v>0.3091578956776017</v>
       </c>
     </row>
     <row r="7">
@@ -4178,67 +4178,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>30366</v>
+        <v>40957</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>24254</v>
+        <v>32931</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>37210</v>
+        <v>48106</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4687829967335901</v>
+        <v>0.5148201699740569</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.374427128385027</v>
+        <v>0.4139350343590036</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5744298641034282</v>
+        <v>0.6046789588653119</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>33149</v>
+        <v>39551</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>27236</v>
+        <v>33060</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>38891</v>
+        <v>45269</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.6232318862557191</v>
+        <v>0.6258791224775043</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5120656486492724</v>
+        <v>0.5231725801187913</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.7311824639645218</v>
+        <v>0.716371492152183</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>63515</v>
+        <v>80507</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>54249</v>
+        <v>70199</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>72269</v>
+        <v>89069</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5384213751212017</v>
+        <v>0.5639838570999981</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4598681186962992</v>
+        <v>0.4917726125452587</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.6126241678409623</v>
+        <v>0.6239634915822833</v>
       </c>
     </row>
     <row r="8">
@@ -4255,19 +4255,19 @@
         <v>4356</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1524</v>
+        <v>1513</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9630</v>
+        <v>9542</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.06725256008742317</v>
+        <v>0.05475929983070538</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02352358268777719</v>
+        <v>0.01901697741890577</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1486703028776765</v>
+        <v>0.1199457369308822</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>2</v>
@@ -4279,16 +4279,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>4535</v>
+        <v>4460</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02439107941384966</v>
+        <v>0.02053014598379068</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.08526466632232818</v>
+        <v>0.07057691335363904</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>7</v>
@@ -4297,19 +4297,19 @@
         <v>5654</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>2597</v>
+        <v>2494</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>11348</v>
+        <v>11453</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.0479270471709191</v>
+        <v>0.03960670409320117</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02201818111046345</v>
+        <v>0.01747339469442712</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.09620036764956404</v>
+        <v>0.080235548754212</v>
       </c>
     </row>
     <row r="9">
@@ -4320,16 +4320,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>64777</v>
+        <v>79556</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -4341,16 +4341,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>53189</v>
+        <v>63192</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -4362,16 +4362,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>117966</v>
+        <v>142747</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -4401,19 +4401,19 @@
         <v>5475</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2673</v>
+        <v>2734</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>10449</v>
+        <v>10512</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.06630553099304749</v>
+        <v>0.05790641873111217</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.03237216299438778</v>
+        <v>0.02891902121416421</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1265573099397439</v>
+        <v>0.1111825754862205</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>6</v>
@@ -4422,19 +4422,19 @@
         <v>3763</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1684</v>
+        <v>1271</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>7946</v>
+        <v>7409</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.05386766801395888</v>
+        <v>0.04547957554858754</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.02410633136827224</v>
+        <v>0.01536526964321849</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1137357222084112</v>
+        <v>0.08953748845106052</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>14</v>
@@ -4443,19 +4443,19 @@
         <v>9238</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>5481</v>
+        <v>5395</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>14722</v>
+        <v>15079</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.06060491845049215</v>
+        <v>0.05210637419149441</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.03596075204899627</v>
+        <v>0.03043170273307064</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.09658183573021988</v>
+        <v>0.08505349332603744</v>
       </c>
     </row>
     <row r="11">
@@ -4466,67 +4466,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>6824</v>
+        <v>8300</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3451</v>
+        <v>4183</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>11794</v>
+        <v>14173</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.08264497524892321</v>
+        <v>0.08779243153582991</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.04179721011123893</v>
+        <v>0.04424296814808597</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1428370289279989</v>
+        <v>0.1499123009082861</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1015</v>
+        <v>3054</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0</v>
+        <v>1036</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>3159</v>
+        <v>6959</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.01452371758973675</v>
+        <v>0.0369043457180783</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0</v>
+        <v>0.01252301572802733</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.04521121913286661</v>
+        <v>0.0841003363233262</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>7838</v>
+        <v>11354</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>4348</v>
+        <v>6916</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>13287</v>
+        <v>17854</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.05142314104159239</v>
+        <v>0.06404117307512024</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.02852394029995323</v>
+        <v>0.03900849470804151</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.08717095442272753</v>
+        <v>0.1007066056663558</v>
       </c>
     </row>
     <row r="12">
@@ -4537,67 +4537,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>18286</v>
+        <v>22606</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>12342</v>
+        <v>16643</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>24730</v>
+        <v>30218</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2214720901419751</v>
+        <v>0.2391066871973292</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1494764603519071</v>
+        <v>0.1760338738377524</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2995114911010628</v>
+        <v>0.3196200893460937</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9492</v>
+        <v>10105</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>5462</v>
+        <v>5993</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>15476</v>
+        <v>16091</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1358660983266325</v>
+        <v>0.1221199402911119</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.07818837295270942</v>
+        <v>0.07242662748300217</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2215259129745695</v>
+        <v>0.1944537336492274</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>27778</v>
+        <v>32711</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>20859</v>
+        <v>25150</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>36654</v>
+        <v>42167</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.1822365243956003</v>
+        <v>0.1845048601174447</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.136841370214825</v>
+        <v>0.1418577691980408</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2404664728930131</v>
+        <v>0.2378366364618517</v>
       </c>
     </row>
     <row r="13">
@@ -4608,67 +4608,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>42690</v>
+        <v>48870</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>35087</v>
+        <v>41253</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>50277</v>
+        <v>56165</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5170330576924954</v>
+        <v>0.5169064325137372</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4249468754580271</v>
+        <v>0.4363341036348403</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.6089243183978851</v>
+        <v>0.5940636575301365</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>53126</v>
+        <v>63359</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>46773</v>
+        <v>55963</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>58025</v>
+        <v>68817</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.760427500635299</v>
+        <v>0.7656802586823838</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.669489615701251</v>
+        <v>0.6763071001114557</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.8305594354004207</v>
+        <v>0.8316475591963101</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>95816</v>
+        <v>112229</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>85762</v>
+        <v>101539</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>105573</v>
+        <v>121985</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.6285873831068188</v>
+        <v>0.6330179220429822</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5626295312433268</v>
+        <v>0.5727209394958732</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.6925989164829468</v>
+        <v>0.6880460104488274</v>
       </c>
     </row>
     <row r="14">
@@ -4682,22 +4682,22 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>9292</v>
+        <v>9293</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5526</v>
+        <v>5198</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>15470</v>
+        <v>14953</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.1125443459235588</v>
+        <v>0.09828803002199141</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.06693143639318207</v>
+        <v>0.05497919067753664</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.187365166341368</v>
+        <v>0.1581594599652083</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>4</v>
@@ -4706,19 +4706,19 @@
         <v>2467</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>5711</v>
+        <v>5987</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03531501543437284</v>
+        <v>0.02981587975983846</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.009070139417535516</v>
+        <v>0.00784933606303481</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.08174393245508636</v>
+        <v>0.07235737545116531</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>17</v>
@@ -4727,19 +4727,19 @@
         <v>11760</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>7250</v>
+        <v>7064</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>17916</v>
+        <v>17992</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.07714803300549633</v>
+        <v>0.0663296705729584</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.04756052463156824</v>
+        <v>0.03984111140734944</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.1175331896409237</v>
+        <v>0.1014849110987013</v>
       </c>
     </row>
     <row r="15">
@@ -4750,16 +4750,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>82567</v>
+        <v>94544</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4771,16 +4771,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>69863</v>
+        <v>82748</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4792,16 +4792,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>152430</v>
+        <v>177292</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4831,19 +4831,19 @@
         <v>6002</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3100</v>
+        <v>3187</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>10546</v>
+        <v>10618</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1049693301319807</v>
+        <v>0.0930311131311289</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.05422053367397906</v>
+        <v>0.04940345546993196</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1844393526413136</v>
+        <v>0.1645851881795807</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>4</v>
@@ -4852,19 +4852,19 @@
         <v>2959</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>765</v>
+        <v>737</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>7250</v>
+        <v>6610</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.06468040946108372</v>
+        <v>0.05606057090104752</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.01672084640001187</v>
+        <v>0.0139563958284556</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1584623208788687</v>
+        <v>0.1252187427855197</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>13</v>
@@ -4873,19 +4873,19 @@
         <v>8961</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>5205</v>
+        <v>5236</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>14752</v>
+        <v>14956</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.08706156445224456</v>
+        <v>0.07639457728855178</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.05056885792692152</v>
+        <v>0.04463435033973809</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1433202109182435</v>
+        <v>0.1275029130367897</v>
       </c>
     </row>
     <row r="17">
@@ -4896,67 +4896,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>9739</v>
+        <v>11016</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>5786</v>
+        <v>6466</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>15366</v>
+        <v>16405</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1703336731078257</v>
+        <v>0.1707445991705404</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1011894547134474</v>
+        <v>0.1002282647911864</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2687326420844937</v>
+        <v>0.2542834047650607</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1732</v>
+        <v>2905</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>557</v>
+        <v>1125</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>4858</v>
+        <v>6547</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.03784857568942568</v>
+        <v>0.0550320393048967</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.01218524112612253</v>
+        <v>0.02131962986951393</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1061894832772601</v>
+        <v>0.1240333084188057</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>11471</v>
+        <v>13920</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>6581</v>
+        <v>9120</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>17024</v>
+        <v>20221</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1114462161812488</v>
+        <v>0.1186745987453155</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.06393581402244343</v>
+        <v>0.0777502889353877</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1654015355209743</v>
+        <v>0.1723856176533594</v>
       </c>
     </row>
     <row r="18">
@@ -4967,67 +4967,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>10866</v>
+        <v>14193</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6247</v>
+        <v>9153</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>16150</v>
+        <v>20350</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.1900361584589482</v>
+        <v>0.2200013744874698</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1092522908447779</v>
+        <v>0.1418706105761804</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.2824460668625763</v>
+        <v>0.3154309999426699</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>9447</v>
+        <v>10153</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>5527</v>
+        <v>6272</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>14662</v>
+        <v>15739</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2065020146513741</v>
+        <v>0.1923466572224818</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1208037743721088</v>
+        <v>0.1188331133924078</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3204860485280482</v>
+        <v>0.29817962393847</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>20313</v>
+        <v>24346</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>14399</v>
+        <v>17858</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>27083</v>
+        <v>31837</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.1973549619786264</v>
+        <v>0.2075569074268552</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1398934348065005</v>
+        <v>0.1522435484168551</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2631253061919921</v>
+        <v>0.2714195334188667</v>
       </c>
     </row>
     <row r="19">
@@ -5038,67 +5038,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>28273</v>
+        <v>31007</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>22394</v>
+        <v>25233</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>34456</v>
+        <v>37276</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.494479331812327</v>
+        <v>0.4806112705410477</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.391661361182926</v>
+        <v>0.391114411310607</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6026085167506753</v>
+        <v>0.5777912379301279</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>27492</v>
+        <v>32648</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>21613</v>
+        <v>26635</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>32278</v>
+        <v>38169</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.6009201501387239</v>
+        <v>0.6185125262387164</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4724083177111341</v>
+        <v>0.5045955728142408</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.7055402850560551</v>
+        <v>0.7231249833856033</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>55765</v>
+        <v>63654</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>47974</v>
+        <v>54980</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>64118</v>
+        <v>72312</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5417905330460046</v>
+        <v>0.5426660591582394</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4660894135632896</v>
+        <v>0.4687209121075634</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.6229415838394038</v>
+        <v>0.6164785189047506</v>
       </c>
     </row>
     <row r="20">
@@ -5115,19 +5115,19 @@
         <v>2297</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>6262</v>
+        <v>6358</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.04018150648891838</v>
+        <v>0.03561164266981324</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01245607740769527</v>
+        <v>0.0110885561049761</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1095091455656911</v>
+        <v>0.09855517936085605</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>6</v>
@@ -5136,19 +5136,19 @@
         <v>4120</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1543</v>
+        <v>1383</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>7475</v>
+        <v>7924</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.09004885005939257</v>
+        <v>0.07804820633285757</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.03372969708942765</v>
+        <v>0.02619732585986495</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1633859994885039</v>
+        <v>0.1501231787770796</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>9</v>
@@ -5157,19 +5157,19 @@
         <v>6417</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>3029</v>
+        <v>2870</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>11803</v>
+        <v>11624</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.06234672434187572</v>
+        <v>0.05470785738103816</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02942913476031838</v>
+        <v>0.02446663371838627</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.1146715095814205</v>
+        <v>0.09909971124186306</v>
       </c>
     </row>
     <row r="21">
@@ -5180,16 +5180,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>57178</v>
+        <v>64515</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -5201,16 +5201,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>45750</v>
+        <v>52784</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -5222,16 +5222,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>102928</v>
+        <v>117299</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -5261,19 +5261,19 @@
         <v>15621</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>10315</v>
+        <v>10491</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>23110</v>
+        <v>23128</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1079497147567665</v>
+        <v>0.08599638927839703</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.07128098174546499</v>
+        <v>0.05775376828089452</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1597014868150644</v>
+        <v>0.1273238697692325</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>13</v>
@@ -5282,19 +5282,19 @@
         <v>8121</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>4656</v>
+        <v>4751</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>13092</v>
+        <v>14049</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.05389285570871446</v>
+        <v>0.04512387817541721</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.03089591122371788</v>
+        <v>0.02639660947724272</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.08688343398183609</v>
+        <v>0.07806485317394533</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>36</v>
@@ -5303,19 +5303,19 @@
         <v>23742</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>17060</v>
+        <v>16774</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>31999</v>
+        <v>32393</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.0803738660823546</v>
+        <v>0.06565476704708345</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.05775293605363741</v>
+        <v>0.04638480809764049</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.108325563287449</v>
+        <v>0.08957649848936937</v>
       </c>
     </row>
     <row r="23">
@@ -5326,67 +5326,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>15015</v>
+        <v>21687</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10030</v>
+        <v>14722</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>22829</v>
+        <v>30413</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1037587252791183</v>
+        <v>0.1193926525782718</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.06931371041991764</v>
+        <v>0.08105002665868898</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1577583023667298</v>
+        <v>0.167427622845545</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>15451</v>
+        <v>16650</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>10219</v>
+        <v>11240</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>22593</v>
+        <v>23385</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1025334487803324</v>
+        <v>0.09251175722377851</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.06781429063311298</v>
+        <v>0.06245172504202725</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1499318527356166</v>
+        <v>0.1299385147894784</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>30465</v>
+        <v>38337</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>23062</v>
+        <v>28850</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>40914</v>
+        <v>48364</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1031336789869392</v>
+        <v>0.1060144430241074</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.07807089314625842</v>
+        <v>0.07978126369476497</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1385054442857737</v>
+        <v>0.1337429732494313</v>
       </c>
     </row>
     <row r="24">
@@ -5397,67 +5397,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>33685</v>
+        <v>46828</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>25138</v>
+        <v>37643</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>42176</v>
+        <v>57095</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.232779258333639</v>
+        <v>0.2577948757028589</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1737201408197097</v>
+        <v>0.2072310130039272</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.2914598203112614</v>
+        <v>0.3143182358735303</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>36769</v>
+        <v>43934</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>28159</v>
+        <v>34856</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>45817</v>
+        <v>53451</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2440071604420838</v>
+        <v>0.244118419733915</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1868672673866144</v>
+        <v>0.1936740566621659</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3040510898918027</v>
+        <v>0.2969949577350241</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>70454</v>
+        <v>90762</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>58841</v>
+        <v>77966</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>82807</v>
+        <v>106289</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2385069113073043</v>
+        <v>0.2509883132168274</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.1991954244404925</v>
+        <v>0.2156030989628325</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2803265392755234</v>
+        <v>0.2939263518135325</v>
       </c>
     </row>
     <row r="25">
@@ -5468,67 +5468,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>73497</v>
+        <v>90622</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>64003</v>
+        <v>80020</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>83757</v>
+        <v>101358</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5079062546245037</v>
+        <v>0.4988914972800963</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4422948961844931</v>
+        <v>0.4405268761407228</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5788079721508235</v>
+        <v>0.5579919429008984</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>84743</v>
+        <v>105662</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>74365</v>
+        <v>94802</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>94633</v>
+        <v>115967</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.5623709984404617</v>
+        <v>0.5871025429926008</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4935022534418771</v>
+        <v>0.5267587444685186</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.628002552730756</v>
+        <v>0.6443590256018348</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>158240</v>
+        <v>196284</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>144088</v>
+        <v>179786</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>172274</v>
+        <v>211993</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5356901762212875</v>
+        <v>0.5427927825226877</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4877791436386096</v>
+        <v>0.4971695738782376</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5831974190161267</v>
+        <v>0.5862316793720765</v>
       </c>
     </row>
     <row r="26">
@@ -5545,19 +5545,19 @@
         <v>6889</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3410</v>
+        <v>3423</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>11806</v>
+        <v>12379</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.04760604700597258</v>
+        <v>0.03792458516037597</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.02356649028540463</v>
+        <v>0.01884353826464539</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.08158810705538942</v>
+        <v>0.06814673955796778</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>9</v>
@@ -5566,19 +5566,19 @@
         <v>5605</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>2590</v>
+        <v>2819</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>10468</v>
+        <v>10088</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03719553662840765</v>
+        <v>0.03114340187428846</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01718721818712025</v>
+        <v>0.01566329584136126</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.06947011229504199</v>
+        <v>0.05605473165323903</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>19</v>
@@ -5587,19 +5587,19 @@
         <v>12494</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>7449</v>
+        <v>7482</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>18681</v>
+        <v>18390</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.04229536740211442</v>
+        <v>0.03454969418929411</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.02521653724700662</v>
+        <v>0.02069072412623524</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.06323997731549433</v>
+        <v>0.0508540168103404</v>
       </c>
     </row>
     <row r="27">
@@ -5610,16 +5610,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>144706</v>
+        <v>181647</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -5631,16 +5631,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>150689</v>
+        <v>179972</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -5652,16 +5652,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>433</v>
+        <v>529</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>295395</v>
+        <v>361619</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -5691,19 +5691,19 @@
         <v>7758</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4001</v>
+        <v>3918</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>13700</v>
+        <v>13773</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.07674959693870657</v>
+        <v>0.06272826332471322</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.03957722223225683</v>
+        <v>0.0316828709274132</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1355327572103362</v>
+        <v>0.1113600593153255</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>10</v>
@@ -5712,19 +5712,19 @@
         <v>6170</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>3312</v>
+        <v>3255</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>10736</v>
+        <v>11017</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.06334984383876453</v>
+        <v>0.05133876051754264</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.034012815696622</v>
+        <v>0.02708412424224934</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1102336910903291</v>
+        <v>0.09167229469686514</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>20</v>
@@ -5733,19 +5733,19 @@
         <v>13928</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>8894</v>
+        <v>8883</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>22225</v>
+        <v>22132</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.07017444956374599</v>
+        <v>0.05711536032567311</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.04481037183996175</v>
+        <v>0.03642599546132638</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1119825407987107</v>
+        <v>0.09076173298052538</v>
       </c>
     </row>
     <row r="29">
@@ -5756,67 +5756,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>15109</v>
+        <v>16939</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>9900</v>
+        <v>11164</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>21658</v>
+        <v>24491</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1494693338925117</v>
+        <v>0.1369600201488239</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09793877721134013</v>
+        <v>0.09026354725580346</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.2142568507683136</v>
+        <v>0.1980203014971485</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>8409</v>
+        <v>9779</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>4527</v>
+        <v>6032</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>13454</v>
+        <v>16089</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.08634866749223338</v>
+        <v>0.08137615128317724</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.04648582248444411</v>
+        <v>0.05019557221954708</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1381422575071437</v>
+        <v>0.1338830327739915</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>23518</v>
+        <v>26718</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>16008</v>
+        <v>19997</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>30937</v>
+        <v>35713</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1184965479842887</v>
+        <v>0.1095675281729828</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.080657795934351</v>
+        <v>0.08200628076420247</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1558748833270488</v>
+        <v>0.146454685524859</v>
       </c>
     </row>
     <row r="30">
@@ -5827,67 +5827,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>25300</v>
+        <v>29453</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>18554</v>
+        <v>22391</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>34176</v>
+        <v>38698</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2502858692802893</v>
+        <v>0.2381457274857446</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.1835480181472983</v>
+        <v>0.1810412916607716</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.3380986663607705</v>
+        <v>0.3128912297204771</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>20447</v>
+        <v>27932</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>14804</v>
+        <v>20383</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>27889</v>
+        <v>36500</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2099547079017996</v>
+        <v>0.2324282219145473</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1520108300219916</v>
+        <v>0.1696121958185827</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2863664288379769</v>
+        <v>0.3037263666288866</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>45747</v>
+        <v>57385</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>35875</v>
+        <v>46386</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>56054</v>
+        <v>68026</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2304957039026873</v>
+        <v>0.2353280624207343</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.1807559023304772</v>
+        <v>0.1902208621395662</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2824297589826392</v>
+        <v>0.2789648632234639</v>
       </c>
     </row>
     <row r="31">
@@ -5898,67 +5898,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>46410</v>
+        <v>63021</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>37946</v>
+        <v>53397</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>55430</v>
+        <v>72345</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4591263122638286</v>
+        <v>0.5095566113515637</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3753893213728463</v>
+        <v>0.4317413296514682</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5483517159077935</v>
+        <v>0.5849442383523272</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>60519</v>
+        <v>74449</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>52120</v>
+        <v>65840</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>67541</v>
+        <v>83766</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6214145087262692</v>
+        <v>0.6195141389555822</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.53517286559802</v>
+        <v>0.5478746591006196</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.6935186996121663</v>
+        <v>0.6970388978511647</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>106929</v>
+        <v>137470</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>95946</v>
+        <v>124736</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>119042</v>
+        <v>150774</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5387597802089745</v>
+        <v>0.5637451871748268</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.4834223784329704</v>
+        <v>0.511525345375164</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5997899195775779</v>
+        <v>0.6182997531335126</v>
       </c>
     </row>
     <row r="32">
@@ -5975,19 +5975,19 @@
         <v>6507</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3076</v>
+        <v>2882</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>11611</v>
+        <v>11276</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.06436888762466386</v>
+        <v>0.05260937768915448</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.03043151873387208</v>
+        <v>0.02330262302047134</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.1148631045478534</v>
+        <v>0.09117241113255824</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>3</v>
@@ -5996,19 +5996,19 @@
         <v>1844</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>5104</v>
+        <v>5041</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01893227204093317</v>
+        <v>0.01534272732915062</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.006050767044884218</v>
+        <v>0.004823067068140466</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05240642968460988</v>
+        <v>0.04194429634874007</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>12</v>
@@ -6017,19 +6017,19 @@
         <v>8350</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>4221</v>
+        <v>4553</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>13865</v>
+        <v>13953</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.04207351834030354</v>
+        <v>0.03424386190578301</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.02126761435656574</v>
+        <v>0.01866946741542169</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06985897850548757</v>
+        <v>0.05721713776237485</v>
       </c>
     </row>
     <row r="33">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>101084</v>
+        <v>123678</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -6061,16 +6061,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>97389</v>
+        <v>120174</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -6082,16 +6082,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>198472</v>
+        <v>243852</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -6121,19 +6121,19 @@
         <v>5398</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2667</v>
+        <v>2632</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>10155</v>
+        <v>9587</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.107304095190453</v>
+        <v>0.09259463592782155</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.05301119379069182</v>
+        <v>0.04515397766415578</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.2018725868568817</v>
+        <v>0.1644460727588535</v>
       </c>
       <c r="J34" s="5" t="n">
         <v>4</v>
@@ -6142,19 +6142,19 @@
         <v>2423</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>5432</v>
+        <v>5948</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.05539227259189435</v>
+        <v>0.0498368064823151</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.01400216583719426</v>
+        <v>0.01262091812297975</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1241871995954053</v>
+        <v>0.1223426932739089</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>12</v>
@@ -6163,19 +6163,19 @@
         <v>7821</v>
       </c>
       <c r="S34" s="5" t="n">
-        <v>4465</v>
+        <v>4331</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>13208</v>
+        <v>13250</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>0.08315949778807538</v>
+        <v>0.07315102656069732</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>0.04746951312989095</v>
+        <v>0.04050797773196407</v>
       </c>
       <c r="W34" s="6" t="n">
-        <v>0.1404342321673664</v>
+        <v>0.1239235819743534</v>
       </c>
     </row>
     <row r="35">
@@ -6186,25 +6186,25 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>6276</v>
+        <v>8235</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2748</v>
+        <v>4756</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>10908</v>
+        <v>13093</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.1247651499759299</v>
+        <v>0.1412525229834155</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.05461615688739949</v>
+        <v>0.08157276652179705</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.2168422398280613</v>
+        <v>0.2245849080455853</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>6</v>
@@ -6213,40 +6213,40 @@
         <v>4887</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>1977</v>
+        <v>1805</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>9758</v>
+        <v>9834</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.1117268746420144</v>
+        <v>0.1005214332228489</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.04520508331249885</v>
+        <v>0.03713220322661376</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.223082886790943</v>
+        <v>0.2022686009850638</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R35" s="5" t="n">
-        <v>11164</v>
+        <v>13122</v>
       </c>
       <c r="S35" s="5" t="n">
-        <v>6769</v>
+        <v>7865</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>17756</v>
+        <v>20116</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0.1187009454652703</v>
+        <v>0.122730549144424</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>0.07196918240929441</v>
+        <v>0.07356502142832309</v>
       </c>
       <c r="W35" s="6" t="n">
-        <v>0.1887915187889457</v>
+        <v>0.1881470994819343</v>
       </c>
     </row>
     <row r="36">
@@ -6257,67 +6257,67 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>12902</v>
+        <v>14464</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>7921</v>
+        <v>9598</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>18210</v>
+        <v>20288</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.2564713029406121</v>
+        <v>0.2481093918843837</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.1574467895289089</v>
+        <v>0.164643240706893</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.3619891525584735</v>
+        <v>0.3480110098879122</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>9922</v>
+        <v>10558</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>5949</v>
+        <v>6064</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>15165</v>
+        <v>15400</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.2268311988875127</v>
+        <v>0.2171594768952095</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.1360041094442007</v>
+        <v>0.1247269274664136</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.346693642322472</v>
+        <v>0.3167384111771109</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R36" s="5" t="n">
-        <v>22825</v>
+        <v>25023</v>
       </c>
       <c r="S36" s="5" t="n">
-        <v>15744</v>
+        <v>18154</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>30169</v>
+        <v>32759</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>0.2426854571832617</v>
+        <v>0.2340352897889498</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>0.1673967011328331</v>
+        <v>0.1697954164894983</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>0.3207746757121456</v>
+        <v>0.3063983001825279</v>
       </c>
     </row>
     <row r="37">
@@ -6328,67 +6328,67 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>24271</v>
+        <v>28742</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>18085</v>
+        <v>22075</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>30133</v>
+        <v>34711</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.4824631093855582</v>
+        <v>0.4930219831275251</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.3595012913318729</v>
+        <v>0.3786529756527189</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5989937053941298</v>
+        <v>0.5954008269794459</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>25168</v>
+        <v>29409</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>19591</v>
+        <v>23665</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>30235</v>
+        <v>34840</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.5753672427426699</v>
+        <v>0.604877108261626</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.4478693318352982</v>
+        <v>0.4867394696613846</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0.6911916476062709</v>
+        <v>0.716596552068244</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="R37" s="5" t="n">
-        <v>49440</v>
+        <v>58151</v>
       </c>
       <c r="S37" s="5" t="n">
-        <v>40737</v>
+        <v>49633</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>56788</v>
+        <v>67236</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0.5256735532621049</v>
+        <v>0.5438867577669876</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>0.4331455641779346</v>
+        <v>0.4642197037999221</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>0.6038074943506265</v>
+        <v>0.6288514285006347</v>
       </c>
     </row>
     <row r="38">
@@ -6408,16 +6408,16 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>4993</v>
+        <v>4384</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.02899634250744673</v>
+        <v>0.02502146607685412</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.09924368573686369</v>
+        <v>0.07519353993154551</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>2</v>
@@ -6429,16 +6429,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>4141</v>
+        <v>4639</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.03068241113590866</v>
+        <v>0.02760517513800052</v>
       </c>
       <c r="O38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.09467586618226854</v>
+        <v>0.09542158749621944</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>4</v>
@@ -6447,19 +6447,19 @@
         <v>2801</v>
       </c>
       <c r="S38" s="5" t="n">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>6528</v>
+        <v>6595</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>0.02978054630128776</v>
+        <v>0.02619637673894128</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>0.007610644007711717</v>
+        <v>0.006636875114353095</v>
       </c>
       <c r="W38" s="6" t="n">
-        <v>0.06940853223448376</v>
+        <v>0.06168332834859176</v>
       </c>
     </row>
     <row r="39">
@@ -6470,37 +6470,37 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>58298</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="D39" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>50306</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>63</v>
-      </c>
       <c r="K39" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>43743</v>
+        <v>48619</v>
       </c>
       <c r="N39" s="6" t="n">
         <v>1</v>
@@ -6512,16 +6512,16 @@
         <v>1</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="R39" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="S39" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>94050</v>
+        <v>106918</v>
       </c>
       <c r="U39" s="6" t="n">
         <v>1</v>
@@ -6551,19 +6551,19 @@
         <v>46157</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>36575</v>
+        <v>36468</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>57809</v>
+        <v>57628</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.09220033977783375</v>
+        <v>0.0766427927369551</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.07305919718188528</v>
+        <v>0.06055457571070301</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.1154756497633274</v>
+        <v>0.09568893517522374</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>42</v>
@@ -6572,19 +6572,19 @@
         <v>26773</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>19431</v>
+        <v>18627</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>34985</v>
+        <v>35033</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.0581244666902854</v>
+        <v>0.04890218439171772</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.04218513831675644</v>
+        <v>0.03402183042834492</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.07595125599213991</v>
+        <v>0.06398788890059814</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>109</v>
@@ -6593,19 +6593,19 @@
         <v>72931</v>
       </c>
       <c r="S40" s="5" t="n">
-        <v>60699</v>
+        <v>60938</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>87305</v>
+        <v>87997</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>0.07587133487276271</v>
+        <v>0.06343297600194185</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>0.06314633425082107</v>
+        <v>0.05300237318835235</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>0.09082566455798677</v>
+        <v>0.07653771120932377</v>
       </c>
     </row>
     <row r="41">
@@ -6616,67 +6616,67 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>59597</v>
+        <v>73386</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>49120</v>
+        <v>61572</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>72456</v>
+        <v>87274</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.1190462158361285</v>
+        <v>0.1218555710266097</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.09811778637919148</v>
+        <v>0.102239087150339</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.1447321274617482</v>
+        <v>0.1449155224520317</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>36110</v>
+        <v>42360</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>26794</v>
+        <v>34064</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>45643</v>
+        <v>53638</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.07839414345921103</v>
+        <v>0.07737122867462702</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.05816944649727956</v>
+        <v>0.06221786418891511</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.09909025744084352</v>
+        <v>0.09797015333787172</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="R41" s="5" t="n">
-        <v>95707</v>
+        <v>115746</v>
       </c>
       <c r="S41" s="5" t="n">
-        <v>81629</v>
+        <v>99522</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>112138</v>
+        <v>132543</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>0.09956592585093807</v>
+        <v>0.1006725456677529</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>0.08492043690827329</v>
+        <v>0.08656169651809151</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>0.1166595947767278</v>
+        <v>0.1152821085701024</v>
       </c>
     </row>
     <row r="42">
@@ -6687,67 +6687,67 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>118556</v>
+        <v>148675</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>103801</v>
+        <v>129962</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>135577</v>
+        <v>165100</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.2368188632755319</v>
+        <v>0.246870434310678</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.2073463068747223</v>
+        <v>0.2157987994121582</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.2708194183241321</v>
+        <v>0.2741444451534538</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>96867</v>
+        <v>116604</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>83168</v>
+        <v>100113</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>111897</v>
+        <v>132637</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.2102954848424583</v>
+        <v>0.2129794011550062</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.1805549386785485</v>
+        <v>0.1828593404498051</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.2429261073895986</v>
+        <v>0.2422633723211226</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="R42" s="5" t="n">
-        <v>215423</v>
+        <v>265279</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>193300</v>
+        <v>241673</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>235769</v>
+        <v>289187</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>0.2241089797922831</v>
+        <v>0.2307318431386663</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>0.2010937443627956</v>
+        <v>0.2102006472162977</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>0.2452758565031693</v>
+        <v>0.2515270904006704</v>
       </c>
     </row>
     <row r="43">
@@ -6758,67 +6758,67 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>351</v>
+        <v>432</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>245508</v>
+        <v>303219</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>225189</v>
+        <v>283529</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>263383</v>
+        <v>327774</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.4904094074745109</v>
+        <v>0.5034875603464406</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.4498222455194504</v>
+        <v>0.4707927731151706</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.5261150009512863</v>
+        <v>0.5442603204897923</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>424</v>
+        <v>516</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>284197</v>
+        <v>345077</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>266530</v>
+        <v>325863</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>300304</v>
+        <v>363526</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.6169845820805001</v>
+        <v>0.630289723201658</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.5786300205216981</v>
+        <v>0.5951946342506246</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.6519540818769117</v>
+        <v>0.6639869485593403</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>775</v>
+        <v>948</v>
       </c>
       <c r="R43" s="5" t="n">
-        <v>529705</v>
+        <v>648296</v>
       </c>
       <c r="S43" s="5" t="n">
-        <v>503155</v>
+        <v>621060</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>555764</v>
+        <v>675656</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0.5510636610483296</v>
+        <v>0.5638695574560426</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>0.5234430006994416</v>
+        <v>0.5401803516549982</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0.5781730881105582</v>
+        <v>0.5876665569965815</v>
       </c>
     </row>
     <row r="44">
@@ -6835,19 +6835,19 @@
         <v>30801</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>23508</v>
+        <v>21932</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>41631</v>
+        <v>40363</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.06152517363599492</v>
+        <v>0.05114364157931656</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.04695893185866644</v>
+        <v>0.03641794294260205</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.08315895399817194</v>
+        <v>0.06702215151682181</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>26</v>
@@ -6856,19 +6856,19 @@
         <v>16675</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>11288</v>
+        <v>11544</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>24817</v>
+        <v>23910</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.03620132292754521</v>
+        <v>0.03045746257699111</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.02450564421659722</v>
+        <v>0.02108484469239929</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.05387634722136398</v>
+        <v>0.04367232384378256</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>68</v>
@@ -6877,19 +6877,19 @@
         <v>47476</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>38159</v>
+        <v>37606</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>59456</v>
+        <v>60662</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0.04939009843568659</v>
+        <v>0.04129307773559636</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0.03969759746064922</v>
+        <v>0.03270882698456119</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>0.06185307382777598</v>
+        <v>0.05276221600387049</v>
       </c>
     </row>
     <row r="45">
@@ -6900,16 +6900,16 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>713</v>
+        <v>857</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>500618</v>
+        <v>602238</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>1</v>
@@ -6921,16 +6921,16 @@
         <v>1</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>688</v>
+        <v>820</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>460622</v>
+        <v>547489</v>
       </c>
       <c r="N45" s="6" t="n">
         <v>1</v>
@@ -6942,16 +6942,16 @@
         <v>1</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>1401</v>
+        <v>1677</v>
       </c>
       <c r="R45" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="S45" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>961241</v>
+        <v>1149727</v>
       </c>
       <c r="U45" s="6" t="n">
         <v>1</v>
@@ -7025,7 +7025,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7215,19 +7215,19 @@
         <v>3367</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1128</v>
+        <v>1209</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7448</v>
+        <v>7603</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.06310634291571902</v>
+        <v>0.060206166449045</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02114738488712776</v>
+        <v>0.0216231258184773</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1395719344869045</v>
+        <v>0.1359297869098957</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>1</v>
@@ -7239,16 +7239,16 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>1647</v>
+        <v>2151</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.009231651962972234</v>
+        <v>0.009035051165578754</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.04149875943767947</v>
+        <v>0.0530421708360722</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>6</v>
@@ -7257,19 +7257,19 @@
         <v>3734</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>1401</v>
+        <v>1500</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>8804</v>
+        <v>8404</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.04012592077880353</v>
+        <v>0.03869777654614458</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.01505427650025983</v>
+        <v>0.01554324363313389</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.09461096480622162</v>
+        <v>0.08709897678228681</v>
       </c>
     </row>
     <row r="5">
@@ -7286,19 +7286,19 @@
         <v>1791</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>486</v>
+        <v>259</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5442</v>
+        <v>5285</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.03355981688266072</v>
+        <v>0.03201750930069595</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.009105478859525323</v>
+        <v>0.004632075585896815</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1019839180230549</v>
+        <v>0.09449012784219912</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>5</v>
@@ -7307,19 +7307,19 @@
         <v>3798</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1394</v>
+        <v>1433</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8927</v>
+        <v>8665</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.09568340748565413</v>
+        <v>0.0936456969778862</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.03513032884860245</v>
+        <v>0.03534325991963765</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2249243809989014</v>
+        <v>0.2136507852246873</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>8</v>
@@ -7328,19 +7328,19 @@
         <v>5589</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>2417</v>
+        <v>2608</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>10559</v>
+        <v>10724</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.06005883360964055</v>
+        <v>0.05792124585651063</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.0259773947272383</v>
+        <v>0.02702817692194597</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1134721458683343</v>
+        <v>0.1111504228918958</v>
       </c>
     </row>
     <row r="6">
@@ -7351,25 +7351,25 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7932</v>
+        <v>9395</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3906</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>13659</v>
+        <v>15402</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.1486413127290312</v>
+        <v>0.1679702285764843</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.0732054033878957</v>
+        <v>0.08939288534373911</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.2559753025187325</v>
+        <v>0.2753762784202571</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>11</v>
@@ -7378,40 +7378,40 @@
         <v>7905</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4073</v>
+        <v>4392</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>13416</v>
+        <v>13148</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.1991569379258851</v>
+        <v>0.1949156154670532</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1026091264472761</v>
+        <v>0.1082897429901001</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3380149606741099</v>
+        <v>0.3242083510191174</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>15836</v>
+        <v>17299</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>10406</v>
+        <v>11507</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>22972</v>
+        <v>24430</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.1701889145993064</v>
+        <v>0.1792959908569503</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1118294413258235</v>
+        <v>0.1192581180779424</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.2468736236131531</v>
+        <v>0.2532015155578904</v>
       </c>
     </row>
     <row r="7">
@@ -7422,67 +7422,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>38314</v>
+        <v>39421</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>31998</v>
+        <v>33029</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>43665</v>
+        <v>45115</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.7180254932765913</v>
+        <v>0.7048241673603975</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.5996615428950105</v>
+        <v>0.5905401292035448</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.8183150546777358</v>
+        <v>0.8066328662534329</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>26152</v>
+        <v>27016</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>20387</v>
+        <v>21451</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>30520</v>
+        <v>31635</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.6588959975985238</v>
+        <v>0.6661602791307151</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5136505896110686</v>
+        <v>0.528948071202758</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.7689436489921402</v>
+        <v>0.7800612827318358</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>64466</v>
+        <v>66437</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>56890</v>
+        <v>58588</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>71695</v>
+        <v>73830</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.6928036173382823</v>
+        <v>0.688572850995697</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.6113804266501602</v>
+        <v>0.6072274282515648</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.770496449861949</v>
+        <v>0.7652004575993939</v>
       </c>
     </row>
     <row r="8">
@@ -7499,19 +7499,19 @@
         <v>1957</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5754</v>
+        <v>6230</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.03666703419599796</v>
+        <v>0.03498192831337714</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.00700325192294945</v>
+        <v>0.006920298179859545</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1078357823254263</v>
+        <v>0.1113822950726588</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>2</v>
@@ -7523,16 +7523,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>4394</v>
+        <v>4526</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.03703200502696474</v>
+        <v>0.03624335725876654</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1106973673275698</v>
+        <v>0.1115920787305938</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>5</v>
@@ -7541,19 +7541,19 @@
         <v>3426</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1005</v>
+        <v>1286</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>7561</v>
+        <v>8174</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.03682271367396719</v>
+        <v>0.0355121357446974</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01080163055653306</v>
+        <v>0.01332360131934347</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.08125634621420567</v>
+        <v>0.08472168165209949</v>
       </c>
     </row>
     <row r="9">
@@ -7564,16 +7564,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>53360</v>
+        <v>55930</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -7585,16 +7585,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>39691</v>
+        <v>40555</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -7606,16 +7606,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>93051</v>
+        <v>96485</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -7648,16 +7648,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4940</v>
+        <v>4356</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.02472578838613027</v>
+        <v>0.02435143158500854</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1184408418338199</v>
+        <v>0.1028460032864254</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>2</v>
@@ -7669,16 +7669,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3168</v>
+        <v>2859</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.02169198404180685</v>
+        <v>0.0202796089374645</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.07919360351718466</v>
+        <v>0.06682544448804889</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>3</v>
@@ -7687,19 +7687,19 @@
         <v>1899</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>5389</v>
+        <v>6006</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.02324064481286953</v>
+        <v>0.02230514566691574</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.005013740261150259</v>
+        <v>0.004832333938896999</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.06595537474777921</v>
+        <v>0.07054294834908657</v>
       </c>
     </row>
     <row r="11">
@@ -7716,19 +7716,19 @@
         <v>6007</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2927</v>
+        <v>2712</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>10689</v>
+        <v>10949</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1439997884401459</v>
+        <v>0.1418195829267437</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.07017069402174383</v>
+        <v>0.06402436474496245</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.2562487187398621</v>
+        <v>0.2585101940706068</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>5</v>
@@ -7737,19 +7737,19 @@
         <v>2595</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>855</v>
+        <v>822</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>6249</v>
+        <v>6230</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.06488111912215724</v>
+        <v>0.06065667947600063</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.0213804016886621</v>
+        <v>0.01921843133021495</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1562282487889373</v>
+        <v>0.1456019797721399</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>14</v>
@@ -7758,19 +7758,19 @@
         <v>8602</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>4819</v>
+        <v>4861</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>14235</v>
+        <v>14272</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1052686871802992</v>
+        <v>0.1010313362915531</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.05897820445551809</v>
+        <v>0.05709382019118382</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1742031996644016</v>
+        <v>0.1676223265648918</v>
       </c>
     </row>
     <row r="12">
@@ -7787,19 +7787,19 @@
         <v>10815</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6068</v>
+        <v>6503</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>16322</v>
+        <v>16834</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.259269111803583</v>
+        <v>0.2553436897378135</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1454827154298559</v>
+        <v>0.153531134424616</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.3913046587933899</v>
+        <v>0.3974583126277384</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>8</v>
@@ -7808,40 +7808,40 @@
         <v>5584</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>2652</v>
+        <v>2543</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>9946</v>
+        <v>10325</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1395891760458987</v>
+        <v>0.1305004602925163</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.06630371856827093</v>
+        <v>0.05943593996865013</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2486371195530448</v>
+        <v>0.2413022329851188</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>16399</v>
+        <v>16398</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>10486</v>
+        <v>10666</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>24445</v>
+        <v>24006</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2006819824880888</v>
+        <v>0.1926039870306668</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1283230305266012</v>
+        <v>0.1252723699831605</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2991509630371009</v>
+        <v>0.2819550629492967</v>
       </c>
     </row>
     <row r="13">
@@ -7852,67 +7852,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>23336</v>
+        <v>23978</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>17941</v>
+        <v>18237</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>29398</v>
+        <v>29800</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.5594588960988397</v>
+        <v>0.5661288374509057</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4301221438603011</v>
+        <v>0.4305965900819291</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.7047922737486997</v>
+        <v>0.7035920733635893</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>28427</v>
+        <v>31212</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>23008</v>
+        <v>25605</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>32519</v>
+        <v>35655</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.7106280954326027</v>
+        <v>0.7294692338512662</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5751722702480344</v>
+        <v>0.5984240445710274</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.8129355216415235</v>
+        <v>0.8333164505174359</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>51763</v>
+        <v>55190</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>43566</v>
+        <v>47252</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>58813</v>
+        <v>62372</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.6334610199620975</v>
+        <v>0.6482152105426596</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5331491352653102</v>
+        <v>0.5549864743696145</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.719746567671563</v>
+        <v>0.7325743894112677</v>
       </c>
     </row>
     <row r="14">
@@ -7932,37 +7932,37 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>3034</v>
+        <v>2970</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.01254641527130084</v>
+        <v>0.01235645829952866</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.072729318564817</v>
+        <v>0.07012476161815462</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>5906</v>
+        <v>5792</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.06320962535753458</v>
+        <v>0.05909401744275242</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.01560151816651329</v>
+        <v>0.01439130305403371</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1476403074277947</v>
+        <v>0.1353634896063829</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>5</v>
@@ -7971,19 +7971,19 @@
         <v>3052</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>1220</v>
+        <v>1077</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>7529</v>
+        <v>6962</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.03734766555664489</v>
+        <v>0.03584432046820476</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.01492514089367174</v>
+        <v>0.01264617642165306</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.09213234784076904</v>
+        <v>0.08176787588111863</v>
       </c>
     </row>
     <row r="15">
@@ -7994,16 +7994,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>41712</v>
+        <v>42354</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -8015,16 +8015,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>40002</v>
+        <v>42787</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -8036,16 +8036,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>81714</v>
+        <v>85141</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -8075,19 +8075,19 @@
         <v>2770</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>996</v>
+        <v>972</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>6151</v>
+        <v>5831</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.09996258122852057</v>
+        <v>0.09446437669521529</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.03594839677913356</v>
+        <v>0.0331343948509794</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2219616510730597</v>
+        <v>0.1988548387051394</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>2</v>
@@ -8099,16 +8099,16 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>3779</v>
+        <v>3695</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.06678590283160386</v>
+        <v>0.05839277247953491</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2214185415880884</v>
+        <v>0.1892508151210604</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>7</v>
@@ -8117,19 +8117,19 @@
         <v>3910</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>1614</v>
+        <v>1781</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>7960</v>
+        <v>8055</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.08731685092535754</v>
+        <v>0.08004804292068908</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.03605021021508095</v>
+        <v>0.03645400801625149</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1777657276954628</v>
+        <v>0.1649027565184411</v>
       </c>
     </row>
     <row r="17">
@@ -8149,58 +8149,58 @@
         <v>1666</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>8256</v>
+        <v>8329</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1494486123567066</v>
+        <v>0.1412285461293513</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.06011667287374992</v>
+        <v>0.05680080661899699</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2979347023437974</v>
+        <v>0.2840275469755222</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>856</v>
+        <v>1362</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>4068</v>
+        <v>3996</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.05017050948931064</v>
+        <v>0.06979023815792249</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0</v>
+        <v>0.01195317082823379</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2383693067354459</v>
+        <v>0.2047120505481762</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>4998</v>
+        <v>5504</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>2298</v>
+        <v>2826</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>9710</v>
+        <v>10691</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.111607448788402</v>
+        <v>0.1126775982467555</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.05131055274967533</v>
+        <v>0.05785803228622378</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2168371656904639</v>
+        <v>0.2188815331221674</v>
       </c>
     </row>
     <row r="18">
@@ -8217,61 +8217,61 @@
         <v>5923</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2785</v>
+        <v>2589</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10400</v>
+        <v>11125</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.213743385106999</v>
+        <v>0.2019869374991413</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1005102731342624</v>
+        <v>0.08829200116483835</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3753055778331212</v>
+        <v>0.3793714966023234</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1931</v>
+        <v>2300</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>456</v>
+        <v>517</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>4794</v>
+        <v>5672</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1131264844660491</v>
+        <v>0.1178157225841995</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.0266982902479575</v>
+        <v>0.02648035700495485</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2809037912884375</v>
+        <v>0.2905412343171799</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>7854</v>
+        <v>8223</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>4008</v>
+        <v>4078</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>13795</v>
+        <v>13317</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.1753919210386777</v>
+        <v>0.1683471714059634</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.08949987180478568</v>
+        <v>0.08349160883432623</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.3080717167738627</v>
+        <v>0.2726380609573777</v>
       </c>
     </row>
     <row r="19">
@@ -8282,67 +8282,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>12590</v>
+        <v>14203</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>8394</v>
+        <v>9533</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>17053</v>
+        <v>18668</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.4543162916838301</v>
+        <v>0.4843303289559966</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3029033948932673</v>
+        <v>0.3251020414783228</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6154017219612823</v>
+        <v>0.6366265941438022</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>11384</v>
+        <v>12963</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>7781</v>
+        <v>8942</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>14082</v>
+        <v>15937</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.6669786986776297</v>
+        <v>0.6639993564860126</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.455854021565804</v>
+        <v>0.4580353827363963</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.8250622395888463</v>
+        <v>0.8163782810865869</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>23974</v>
+        <v>27165</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>18447</v>
+        <v>21528</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>29056</v>
+        <v>32795</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5353753842274347</v>
+        <v>0.5561366354992275</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4119497914515384</v>
+        <v>0.440729470238956</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.648868004138765</v>
+        <v>0.6713923036052549</v>
       </c>
     </row>
     <row r="20">
@@ -8359,19 +8359,19 @@
         <v>2287</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>5129</v>
+        <v>5472</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.0825291296239437</v>
+        <v>0.07798981072029536</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02167062144481792</v>
+        <v>0.0210969859176187</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1850773258509446</v>
+        <v>0.1866058615123499</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>3</v>
@@ -8380,19 +8380,19 @@
         <v>1757</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>5088</v>
+        <v>4667</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.1029384045354066</v>
+        <v>0.09000191029233065</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.0209727054553139</v>
+        <v>0.01853661965648066</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.2981243903807787</v>
+        <v>0.2390427328934573</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>7</v>
@@ -8401,19 +8401,19 @@
         <v>4044</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>1767</v>
+        <v>1634</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>7513</v>
+        <v>7875</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.09030839502012805</v>
+        <v>0.08279055192736445</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.03945964166447111</v>
+        <v>0.03345101517169061</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.167775223766409</v>
+        <v>0.1612187952853171</v>
       </c>
     </row>
     <row r="21">
@@ -8424,16 +8424,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>27711</v>
+        <v>29324</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -8445,16 +8445,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>17068</v>
+        <v>19522</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -8466,16 +8466,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>44779</v>
+        <v>48846</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -8505,19 +8505,19 @@
         <v>6462</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3597</v>
+        <v>3501</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>11319</v>
+        <v>11705</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.08090583343574953</v>
+        <v>0.07633444051426071</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.0450334685471417</v>
+        <v>0.04135293172361538</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1417139891544488</v>
+        <v>0.1382666560418316</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>6</v>
@@ -8526,40 +8526,40 @@
         <v>3339</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1422</v>
+        <v>1354</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>6962</v>
+        <v>6859</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.04460857710745126</v>
+        <v>0.04342169153166616</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.01899686596759808</v>
+        <v>0.01760059227277212</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.09301015573885084</v>
+        <v>0.08919452963525577</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>9801</v>
+        <v>9802</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>6052</v>
+        <v>5901</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>15524</v>
+        <v>15161</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.06334577689394623</v>
+        <v>0.06066801206496897</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.03911558898148184</v>
+        <v>0.03652283564556479</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1003291438127237</v>
+        <v>0.09384237598883002</v>
       </c>
     </row>
     <row r="23">
@@ -8576,19 +8576,19 @@
         <v>10426</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>5943</v>
+        <v>5514</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>17476</v>
+        <v>17370</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.130530488303525</v>
+        <v>0.1231551715317982</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.07440275664253378</v>
+        <v>0.0651286953076238</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.2187945711648241</v>
+        <v>0.2051812058205339</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>9</v>
@@ -8597,19 +8597,19 @@
         <v>4697</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>2443</v>
+        <v>2406</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>8869</v>
+        <v>9147</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.06274299651290197</v>
+        <v>0.06107361447089418</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.03264087840501206</v>
+        <v>0.03129098582597038</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1184846805227804</v>
+        <v>0.1189380049522571</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>22</v>
@@ -8618,19 +8618,19 @@
         <v>15123</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>8956</v>
+        <v>9466</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>22944</v>
+        <v>23119</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.09773593827186491</v>
+        <v>0.09360442594595793</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.05787987685089379</v>
+        <v>0.05859108571747085</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1482857918672647</v>
+        <v>0.1430976770145111</v>
       </c>
     </row>
     <row r="24">
@@ -8641,67 +8641,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>17624</v>
+        <v>19886</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10660</v>
+        <v>12713</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>28779</v>
+        <v>31818</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2206432957190831</v>
+        <v>0.2349062392809962</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1334593156011399</v>
+        <v>0.1501661439684677</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3603003401349288</v>
+        <v>0.3758421193526216</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>13087</v>
+        <v>13912</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>8395</v>
+        <v>8594</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>19000</v>
+        <v>20011</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1748286596626197</v>
+        <v>0.1809111525859929</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1121501980590467</v>
+        <v>0.1117474354674728</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.253825414698944</v>
+        <v>0.2602135316010302</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>30711</v>
+        <v>33799</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>21506</v>
+        <v>25274</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>44058</v>
+        <v>46391</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.1984788766699655</v>
+        <v>0.2092046437452382</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.1389906323061763</v>
+        <v>0.1564362325550328</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2847383329528863</v>
+        <v>0.2871427020653715</v>
       </c>
     </row>
     <row r="25">
@@ -8712,67 +8712,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41421</v>
+        <v>43942</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>32481</v>
+        <v>34636</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>49926</v>
+        <v>53173</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5185835480318132</v>
+        <v>0.5190549754042054</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4066528607120643</v>
+        <v>0.4091311952537494</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.6250637193429553</v>
+        <v>0.6280956389981489</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>48982</v>
+        <v>50203</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>41555</v>
+        <v>42734</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>55349</v>
+        <v>56824</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.6543532187376282</v>
+        <v>0.6528156267672957</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5551303547586385</v>
+        <v>0.5556939545287323</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.73940426182603</v>
+        <v>0.7389195975973428</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>90404</v>
+        <v>94145</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>79535</v>
+        <v>81693</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>101408</v>
+        <v>105157</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5842668347434152</v>
+        <v>0.5827248826191486</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5140261469377334</v>
+        <v>0.5056482518433455</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.6553860784382747</v>
+        <v>0.6508870643633433</v>
       </c>
     </row>
     <row r="26">
@@ -8789,19 +8789,19 @@
         <v>3941</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1577</v>
+        <v>1474</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>8329</v>
+        <v>8786</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.04933683450982927</v>
+        <v>0.04654917326873955</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.01974230008407199</v>
+        <v>0.01741106109731258</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.1042757009133794</v>
+        <v>0.1037888539408485</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>7</v>
@@ -8810,19 +8810,19 @@
         <v>4751</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1959</v>
+        <v>2105</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>9475</v>
+        <v>9768</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.06346654797939895</v>
+        <v>0.06177791464415098</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.02616659615614715</v>
+        <v>0.02737094832199425</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.1265811417620274</v>
+        <v>0.1270204704798748</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>13</v>
@@ -8831,19 +8831,19 @@
         <v>8692</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>4843</v>
+        <v>4630</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>15079</v>
+        <v>14750</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.05617257342080816</v>
+        <v>0.05379803562468622</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.03130142198753354</v>
+        <v>0.02865890127570029</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.09745566209883504</v>
+        <v>0.09129885416588394</v>
       </c>
     </row>
     <row r="27">
@@ -8854,16 +8854,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>79874</v>
+        <v>84657</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -8875,16 +8875,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>74856</v>
+        <v>76902</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -8896,16 +8896,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>154730</v>
+        <v>161560</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -8932,22 +8932,22 @@
         <v>9</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>4757</v>
+        <v>4758</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2154</v>
+        <v>2356</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>9036</v>
+        <v>9080</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.08948050007440658</v>
+        <v>0.08178844480202915</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.04052193845243384</v>
+        <v>0.04050823030982816</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1699488826033101</v>
+        <v>0.1560991992572711</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>4</v>
@@ -8956,19 +8956,19 @@
         <v>1875</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>4899</v>
+        <v>5147</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.05489007511296796</v>
+        <v>0.04878574529552154</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.01242998447962774</v>
+        <v>0.01286125139891691</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1434155424515707</v>
+        <v>0.1339249474783742</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>13</v>
@@ -8977,19 +8977,19 @@
         <v>6633</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>3845</v>
+        <v>3688</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>11581</v>
+        <v>10880</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.07595006212429319</v>
+        <v>0.06865825686848336</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.04403051601114101</v>
+        <v>0.0381737259546162</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1326150104214156</v>
+        <v>0.1126263053056573</v>
       </c>
     </row>
     <row r="29">
@@ -9000,67 +9000,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>9671</v>
+        <v>10126</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5562</v>
+        <v>5749</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>15093</v>
+        <v>16170</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1818960541521005</v>
+        <v>0.1740848907658796</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.1046132861223151</v>
+        <v>0.09883090000456828</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.2838652758383723</v>
+        <v>0.2779905013148525</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5469</v>
+        <v>6861</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>2515</v>
+        <v>3399</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>9877</v>
+        <v>11370</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1601023366338749</v>
+        <v>0.1785188780780036</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.07362642991672128</v>
+        <v>0.08843672565431314</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.2891361584133378</v>
+        <v>0.2958315525753875</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>15140</v>
+        <v>16987</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>9950</v>
+        <v>11039</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>21847</v>
+        <v>24477</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1733711937922933</v>
+        <v>0.175848961207804</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.1139424515444432</v>
+        <v>0.1142705008769158</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.2501771400645325</v>
+        <v>0.2533769855961677</v>
       </c>
     </row>
     <row r="30">
@@ -9071,67 +9071,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>10398</v>
+        <v>12162</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6399</v>
+        <v>7620</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16568</v>
+        <v>18319</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.1955674445464481</v>
+        <v>0.209086332839222</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.1203495251307256</v>
+        <v>0.1309968041534937</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.311610831712603</v>
+        <v>0.3149302756703167</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>8564</v>
+        <v>10872</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>5031</v>
+        <v>6794</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>13290</v>
+        <v>16229</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2507073275648827</v>
+        <v>0.2828708781786066</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1472833451980018</v>
+        <v>0.176771960029334</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.3890546042147493</v>
+        <v>0.4222773183354633</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>18962</v>
+        <v>23034</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>13180</v>
+        <v>16636</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>25966</v>
+        <v>30479</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2171360366232773</v>
+        <v>0.2384416571425056</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.150924810304982</v>
+        <v>0.1722127493287809</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2973368447270198</v>
+        <v>0.3155119148128113</v>
       </c>
     </row>
     <row r="31">
@@ -9142,67 +9142,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>26220</v>
+        <v>29002</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>20251</v>
+        <v>21994</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>32377</v>
+        <v>35522</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4931621547300045</v>
+        <v>0.4985758990131384</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.380893675437489</v>
+        <v>0.3781029348746579</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.608965194382428</v>
+        <v>0.6106755134669396</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>17013</v>
+        <v>17587</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>12344</v>
+        <v>12813</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>21451</v>
+        <v>23070</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.4980416542110701</v>
+        <v>0.4575982146119124</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.3613829496284421</v>
+        <v>0.3333906247107593</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.6279734171157243</v>
+        <v>0.6002684792592232</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>43234</v>
+        <v>46589</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>35173</v>
+        <v>38310</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>50970</v>
+        <v>55529</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.4950708264225254</v>
+        <v>0.4822728478895922</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.402769376116274</v>
+        <v>0.3965717723618888</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5836619679584933</v>
+        <v>0.5748189916157879</v>
       </c>
     </row>
     <row r="32">
@@ -9219,19 +9219,19 @@
         <v>2121</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>5851</v>
+        <v>6816</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.03989384649704036</v>
+        <v>0.03646443257973096</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.01080678170044161</v>
+        <v>0.01002623127903939</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.1100533757937988</v>
+        <v>0.1171833822283142</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>2</v>
@@ -9243,16 +9243,16 @@
         <v>0</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>3828</v>
+        <v>3981</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03625860647720449</v>
+        <v>0.03222628383595593</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.1120539828966043</v>
+        <v>0.1035813850644532</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>5</v>
@@ -9261,19 +9261,19 @@
         <v>3360</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>1226</v>
+        <v>1181</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>7547</v>
+        <v>7054</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.03847188103761073</v>
+        <v>0.03477827689161476</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.01404322259496686</v>
+        <v>0.01222915666799143</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.08642400710404234</v>
+        <v>0.07302541692370264</v>
       </c>
     </row>
     <row r="33">
@@ -9284,16 +9284,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>53168</v>
+        <v>58169</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -9305,16 +9305,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>34159</v>
+        <v>38433</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -9326,16 +9326,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>87328</v>
+        <v>96602</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -9779,19 +9779,19 @@
         <v>20274</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>14368</v>
+        <v>14235</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>28765</v>
+        <v>28499</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.06994278369494551</v>
+        <v>0.06658700981460791</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.04956737631313278</v>
+        <v>0.04675121734740078</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.09923748175867703</v>
+        <v>0.09359953251048898</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>18</v>
@@ -9800,19 +9800,19 @@
         <v>9822</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>5824</v>
+        <v>5989</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>15270</v>
+        <v>15942</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0.04216213697205048</v>
+        <v>0.04002754693881207</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0.02499931298724129</v>
+        <v>0.02440536027135757</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.06554729372089094</v>
+        <v>0.06496877949794974</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>53</v>
@@ -9821,19 +9821,19 @@
         <v>30096</v>
       </c>
       <c r="S40" s="5" t="n">
-        <v>22944</v>
+        <v>22709</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>40154</v>
+        <v>39158</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>0.05756437051750048</v>
+        <v>0.05473444117997027</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>0.04388575254182257</v>
+        <v>0.04129987982951478</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>0.07680264956389476</v>
+        <v>0.0712149106327942</v>
       </c>
     </row>
     <row r="41">
@@ -9844,67 +9844,67 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>36194</v>
+        <v>36649</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>27129</v>
+        <v>27327</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>46615</v>
+        <v>48913</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.1248657424016222</v>
+        <v>0.1203698205646295</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.09359196208196888</v>
+        <v>0.08975129597088077</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.1608164576161448</v>
+        <v>0.1606481151116693</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>17415</v>
+        <v>19313</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>11453</v>
+        <v>13194</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>24688</v>
+        <v>26912</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.07475649321830583</v>
+        <v>0.07870746076450227</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.04916353858000206</v>
+        <v>0.05376766436737247</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0.1059774884933274</v>
+        <v>0.1096758343681683</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="R41" s="5" t="n">
-        <v>53609</v>
+        <v>55963</v>
       </c>
       <c r="S41" s="5" t="n">
-        <v>42206</v>
+        <v>44760</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>65549</v>
+        <v>68994</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>0.1025382207787562</v>
+        <v>0.1017773519849282</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>0.08072758134356964</v>
+        <v>0.08140305508227215</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>0.1253754904034072</v>
+        <v>0.1254768029324564</v>
       </c>
     </row>
     <row r="42">
@@ -9915,67 +9915,67 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>61841</v>
+        <v>67331</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>49135</v>
+        <v>54697</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>77183</v>
+        <v>83365</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.2133427882889448</v>
+        <v>0.2211389886456984</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.1695098407025816</v>
+        <v>0.1796439093899714</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.2662738096023908</v>
+        <v>0.2738009734714986</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>38442</v>
+        <v>41944</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>29189</v>
+        <v>32878</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>48307</v>
+        <v>52764</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0.165016840134406</v>
+        <v>0.1709351349633591</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0.125297036618498</v>
+        <v>0.1339869978542392</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0.2073648251886813</v>
+        <v>0.2150304113446949</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="R42" s="5" t="n">
-        <v>100283</v>
+        <v>109275</v>
       </c>
       <c r="S42" s="5" t="n">
-        <v>85435</v>
+        <v>92594</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>119364</v>
+        <v>127691</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>0.1918098643287668</v>
+        <v>0.1987347471037691</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>0.1634104735216234</v>
+        <v>0.1683973985311137</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>0.2283073853116291</v>
+        <v>0.2322271414163952</v>
       </c>
     </row>
     <row r="43">
@@ -9986,67 +9986,67 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>158260</v>
+        <v>166923</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>142866</v>
+        <v>150667</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>174563</v>
+        <v>181636</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.5459789581434713</v>
+        <v>0.5482352299846754</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.4928692161899203</v>
+        <v>0.4948438730940066</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.602220122912001</v>
+        <v>0.5965555097682032</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>155534</v>
+        <v>162557</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>143982</v>
+        <v>149964</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>167555</v>
+        <v>173900</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.6676488717811202</v>
+        <v>0.6624666497794581</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0.6180593947350441</v>
+        <v>0.6111458538946877</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0.719247745766587</v>
+        <v>0.708695109091933</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="R43" s="5" t="n">
-        <v>313794</v>
+        <v>329480</v>
       </c>
       <c r="S43" s="5" t="n">
-        <v>293058</v>
+        <v>307328</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>333079</v>
+        <v>349685</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0.6001922555261293</v>
+        <v>0.5992127572668118</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>0.560530139875508</v>
+        <v>0.558925680296672</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0.6370776720513593</v>
+        <v>0.6359587466573097</v>
       </c>
     </row>
     <row r="44">
@@ -10063,19 +10063,19 @@
         <v>13296</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>7723</v>
+        <v>8113</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>19471</v>
+        <v>20196</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.04586972747101609</v>
+        <v>0.04366895099038878</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.02664206989768537</v>
+        <v>0.02664447724899708</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.06717106118980959</v>
+        <v>0.06633193733502167</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>18</v>
@@ -10084,19 +10084,19 @@
         <v>11745</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>6822</v>
+        <v>7304</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>17929</v>
+        <v>17914</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0.05041565789411751</v>
+        <v>0.04786320755386839</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0.02928304897517195</v>
+        <v>0.02976432951522099</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.07696087754671931</v>
+        <v>0.07300629074488096</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>38</v>
@@ -10105,19 +10105,19 @@
         <v>25041</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>18221</v>
+        <v>18088</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>34283</v>
+        <v>34420</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0.04789528884884722</v>
+        <v>0.04554070246452065</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0.03485171198922073</v>
+        <v>0.03289578160139357</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>0.06557273667956565</v>
+        <v>0.06259889701063073</v>
       </c>
     </row>
     <row r="45">
@@ -10128,16 +10128,16 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>289865</v>
+        <v>304474</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>1</v>
@@ -10149,16 +10149,16 @@
         <v>1</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>232958</v>
+        <v>245381</v>
       </c>
       <c r="N45" s="6" t="n">
         <v>1</v>
@@ -10170,16 +10170,16 @@
         <v>1</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>753</v>
+        <v>792</v>
       </c>
       <c r="R45" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="S45" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>522823</v>
+        <v>549855</v>
       </c>
       <c r="U45" s="6" t="n">
         <v>1</v>
